--- a/KatalonData/VLinkSmokeData.xlsx
+++ b/KatalonData/VLinkSmokeData.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cloned-Project-Katalon\VPS-Katalon\KatalonData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{D96B97DE-22D2-49C7-B2EE-7B13F16F07D1}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B75DAD-2D41-47E3-A99D-5900C500CD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="7" firstSheet="1" tabRatio="887" windowHeight="14565" windowWidth="18810" xWindow="4410" xr2:uid="{D3A86137-2393-48B3-A2A1-24E657E7CF34}" yWindow="1665"/>
+    <workbookView xWindow="3960" yWindow="3083" windowWidth="21600" windowHeight="11392" tabRatio="887" activeTab="2" xr2:uid="{D3A86137-2393-48B3-A2A1-24E657E7CF34}"/>
   </bookViews>
   <sheets>
-    <sheet name="Auth" r:id="rId1" sheetId="1"/>
-    <sheet name="AuthCapture" r:id="rId2" sheetId="2"/>
-    <sheet name="Sale" r:id="rId3" sheetId="3"/>
-    <sheet name="Sale-Void" r:id="rId4" sheetId="4"/>
-    <sheet name="Sale-Credit" r:id="rId5" sheetId="5"/>
-    <sheet name="Sale-Unencrypted" r:id="rId6" sheetId="6"/>
-    <sheet name="Sale-ZeroDollar" r:id="rId7" sheetId="7"/>
-    <sheet name="Sale-Void-NoTranxID" r:id="rId8" sheetId="8"/>
-    <sheet name="Sale-Credit-Void" r:id="rId9" sheetId="9"/>
-    <sheet name="Auth-Cap-Void" r:id="rId10" sheetId="10"/>
-    <sheet name="Auth-Cap-Credit" r:id="rId11" sheetId="11"/>
-    <sheet name="Sale-Encrypted" r:id="rId12" sheetId="12"/>
-    <sheet name="Sale-MRF" r:id="rId13" sheetId="13"/>
-    <sheet name="Auth-MRF" r:id="rId14" sheetId="14"/>
-    <sheet name="Cap-MRF" r:id="rId15" sheetId="15"/>
-    <sheet name="Void-MRF" r:id="rId16" sheetId="16"/>
-    <sheet name="Credit-MRF" r:id="rId17" sheetId="17"/>
-    <sheet name="Sale-CardNotAccepted" r:id="rId18" sheetId="18"/>
-    <sheet name="Auth-CardNotAccepted" r:id="rId19" sheetId="19"/>
-    <sheet name="CreditClient" r:id="rId20" sheetId="20"/>
+    <sheet name="Auth" sheetId="1" r:id="rId1"/>
+    <sheet name="AuthCapture" sheetId="2" r:id="rId2"/>
+    <sheet name="Sale" sheetId="3" r:id="rId3"/>
+    <sheet name="Sale-Void" sheetId="4" r:id="rId4"/>
+    <sheet name="Sale-Credit" sheetId="5" r:id="rId5"/>
+    <sheet name="Sale-Unencrypted" sheetId="6" r:id="rId6"/>
+    <sheet name="Sale-ZeroDollar" sheetId="7" r:id="rId7"/>
+    <sheet name="Sale-Void-NoTranxID" sheetId="8" r:id="rId8"/>
+    <sheet name="Sale-Credit-Void" sheetId="9" r:id="rId9"/>
+    <sheet name="Auth-Cap-Void" sheetId="10" r:id="rId10"/>
+    <sheet name="Auth-Cap-Credit" sheetId="11" r:id="rId11"/>
+    <sheet name="Sale-Encrypted" sheetId="12" r:id="rId12"/>
+    <sheet name="Sale-MRF" sheetId="13" r:id="rId13"/>
+    <sheet name="Auth-MRF" sheetId="14" r:id="rId14"/>
+    <sheet name="Cap-MRF" sheetId="15" r:id="rId15"/>
+    <sheet name="Void-MRF" sheetId="16" r:id="rId16"/>
+    <sheet name="Credit-MRF" sheetId="17" r:id="rId17"/>
+    <sheet name="Sale-CardNotAccepted" sheetId="18" r:id="rId18"/>
+    <sheet name="Auth-CardNotAccepted" sheetId="19" r:id="rId19"/>
+    <sheet name="CreditClient" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6510" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="295">
   <si>
     <t>Result</t>
   </si>
@@ -450,285 +450,6 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>Wed Feb 15 22:16:49 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:17:31 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:18:13 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:18:55 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:19:37 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:20:20 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:21:03 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:21:46 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:22:29 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:23:11 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:23:54 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:24:36 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:25:19 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:26:02 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:26:44 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:27:27 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:28:09 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:28:51 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:29:34 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:30:16 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:30:59 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:31:40 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:32:23 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:33:05 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:33:48 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:34:31 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:35:13 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:35:56 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:36:38 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:37:21 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed Feb 15 22:38:04 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:16:21 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:17:38 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:18:00 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:18:21 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:18:43 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:19:05 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:19:27 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:19:48 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:20:10 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:20:32 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:20:53 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:21:15 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:21:36 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:21:58 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:22:19 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:22:40 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:23:02 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:23:23 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:23:45 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:24:06 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:24:27 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:24:49 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:25:11 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:25:33 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:25:54 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:26:16 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:26:37 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:26:59 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:27:21 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:27:43 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:28:04 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:28:26 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:28:48 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:29:10 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:29:21 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:29:33 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:29:44 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:29:55 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:30:06 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:30:17 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:30:29 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:30:40 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:30:52 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:31:04 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:31:16 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:31:27 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:31:39 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:31:51 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:32:03 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:32:17 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:32:30 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:32:44 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:32:58 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:33:12 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:33:25 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:33:39 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:59:29 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 19:59:47 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 20:00:05 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 20:00:23 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 20:00:40 EST 2023</t>
-  </si>
-  <si>
-    <t>Thu Feb 16 20:00:57 EST 2023</t>
-  </si>
-  <si>
     <t>Qq2BV1qtr</t>
   </si>
   <si>
@@ -744,147 +465,6 @@
     <t>%B5567080011582687^AHMED/IMTIAZ              ^2603201090300000000000528000015?;5567080011582687=26032010903052800015?</t>
   </si>
   <si>
-    <t>Tue Apr 25 14:00:50 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:01:07 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:01:21 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:01:36 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:01:52 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:02:07 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:02:29 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:02:51 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:03:13 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:03:39 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:04:29 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:04:42 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:05:10 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:05:33 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:05:55 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:06:18 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:07:07 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:07:33 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:07:59 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:08:24 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:10:00 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:10:13 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:10:25 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:10:37 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:10:50 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:11:02 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:11:25 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:11:48 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:12:11 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:12:59 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:13:33 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:14:08 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:14:42 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:15:25 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:16:01 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:16:33 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:17:05 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:17:36 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:18:11 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:18:43 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:19:17 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:19:50 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:20:24 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:21:00 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:21:34 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:21:47 EDT 2023</t>
-  </si>
-  <si>
-    <t>Tue Apr 25 14:21:59 EDT 2023</t>
-  </si>
-  <si>
     <t>Vantiv CPS Dual CF</t>
   </si>
   <si>
@@ -900,12 +480,6 @@
     <t>pwd4494</t>
   </si>
   <si>
-    <t>Thu Jun 15 16:32:37 EDT 2023</t>
-  </si>
-  <si>
-    <t>Thu Jun 15 16:42:31 EDT 2023</t>
-  </si>
-  <si>
     <t>RemID</t>
   </si>
   <si>
@@ -918,2624 +492,460 @@
     <t>4761739001010135</t>
   </si>
   <si>
-    <t>Tue Dec 12 15:13:50 EST 2023</t>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:14:09 EST 2023</t>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:22:59 EST 2023</t>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:29:10 EST 2023</t>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:33:49 EST 2023</t>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:34:07 EST 2023</t>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:34:22 EST 2023</t>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:37:04 EST 2023</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:42:47 EST 2023</t>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:43:03 EST 2023</t>
-  </si>
-  <si>
-    <t>Tue Dec 12 15:43:18 EST 2023</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:30:24 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:30:44 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:31:01 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:31:17 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:31:50 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:32:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:32:32 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:32:56 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:33:20 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:33:45 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:35:51 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:36:06 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:36:21 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:36:36 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:36:51 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:37:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:37:24 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:37:49 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:38:14 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:38:38 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:39:05 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:39:30 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:39:57 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:40:24 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:40:52 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:41:22 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:41:51 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:42:06 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:42:21 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:42:37 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:42:50 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:43:04 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:43:18 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:43:31 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:43:45 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:44:10 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:44:36 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:45:00 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:45:38 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:46:03 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:46:40 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:47:18 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:47:56 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:48:48 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:49:38 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:50:12 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:50:46 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:51:21 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:51:55 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:52:31 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:53:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:53:44 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:54:21 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:54:59 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:55:39 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:55:52 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:56:09 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:56:23 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:57:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:57:50 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:58:32 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:59:14 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed May 15 23:59:57 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:00:39 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:01:21 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:02:04 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:02:46 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:03:28 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:04:11 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:04:53 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:05:35 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:06:18 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:07:01 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:07:44 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:08:27 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:09:09 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:09:52 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:10:34 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:11:17 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:11:59 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:12:42 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:13:25 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:14:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:14:50 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:15:33 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:16:15 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:16:58 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:17:41 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:18:23 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:19:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:19:28 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:19:50 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:20:12 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:20:34 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:20:57 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:21:19 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:21:41 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:22:03 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:22:26 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:22:48 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:23:10 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:23:32 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:23:55 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:24:17 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:24:39 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:25:01 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:25:23 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:25:45 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:26:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:26:29 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:26:51 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:27:14 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:27:36 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:27:58 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:28:22 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:28:44 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:29:06 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:29:29 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:29:51 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:30:13 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:30:35 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:30:58 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:31:10 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:31:21 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:31:33 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:31:44 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:31:56 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:32:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:32:19 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:32:31 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:32:43 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:32:55 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:33:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:33:19 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:33:30 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:33:42 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:33:55 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:34:10 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:34:24 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:34:39 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:34:54 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:35:08 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:35:23 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 00:35:38 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 01:10:11 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 01:10:27 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 01:10:43 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 01:11:00 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 01:11:15 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu May 16 01:11:31 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 20 17:54:40 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 20 17:55:03 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 20 17:55:21 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 20 17:55:41 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 20 17:56:02 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 20 17:56:21 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 18:57:01 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 18:57:22 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 18:57:40 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 18:57:56 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 18:58:17 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 18:58:38 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 18:59:04 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 18:59:29 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 18:59:55 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:00:21 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:00:48 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:01:06 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:01:25 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:01:44 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:02:03 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:02:22 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:02:42 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:03:11 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:03:40 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:04:09 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:04:40 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:05:10 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:05:43 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:06:15 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:06:48 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:07:22 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:07:56 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:08:14 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:08:34 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:08:52 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:09:09 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:09:27 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:09:44 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:10:00 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:10:18 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:10:48 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:11:17 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:11:46 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:12:16 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:12:46 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:13:28 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:14:10 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:14:51 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:15:35 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:16:19 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:16:55 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:17:29 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:18:05 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:18:41 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:19:17 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:19:55 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:20:33 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:21:12 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:21:53 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:22:33 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:22:47 EDT 2024</t>
-  </si>
-  <si>
-    <t>Mon May 27 19:23:02 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 22:42:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 22:45:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 22:47:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 22:49:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 22:49:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 22:50:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 22:52:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 22:56:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:01:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:01:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:01:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:03:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:05:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:07:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:08:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:08:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:08:17 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:12:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:17:13 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:21:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:21:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:21:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:26:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:28:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:32:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:33:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:33:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:35:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:35:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:35:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:35:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:35:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:35:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:35:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:35:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:39:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:44:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:48:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:48:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:48:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Aug 20 23:55:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:02:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:06:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:06:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:06:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:13:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:15:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:20:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:20:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:20:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:27:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:31:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:33:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:33:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:33:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:33:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:33:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:33:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:34:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:34:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:34:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:34:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:34:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:34:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:35:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:35:13 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:35:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:35:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:35:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:35:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:35:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:36:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:36:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:36:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:36:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:36:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:36:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:37:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:37:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:37:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:37:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:37:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:37:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:38:02 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:38:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:38:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:38:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:38:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:38:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:38:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:13 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:17 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:39:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:02 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:40:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:02 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:13 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:17 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 00:41:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 03:34:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 03:34:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 03:34:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 03:34:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 03:34:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 03:34:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 12:50:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:23:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:23:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:23:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:23:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:23:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:23:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:23:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:23:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:23:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:24:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:13 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:25:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:26:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:27:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:27:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:28:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:28:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:28:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:28:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:28:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:29:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:29:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:29:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:29:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:29:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:30:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:30:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:30:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:30:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:30:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:30:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:30:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:30:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 21 22:31:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:26:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:26:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:27:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:27:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:27:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:29:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:29:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:30:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:30:17 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:30:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:51:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:52:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:52:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:52:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:52:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:52:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:52:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:52:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:53:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:53:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:53:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:53:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:53:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:53:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:53:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:54:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:54:13 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:54:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:54:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:54:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:54:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:55:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:55:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:55:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:55:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:55:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:56:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:56:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:56:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:56:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:56:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:56:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:56:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:56:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:56:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:57:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:57:17 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:57:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:57:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:57:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:58:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:58:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:58:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:58:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:59:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:59:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 17:59:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:00:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:00:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:00:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:00:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:01:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:01:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:01:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:01:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:01:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 22 18:01:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 09:37:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 09:37:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 09:37:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:16:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:17:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:17:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:17:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:17:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:17:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:18:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:18:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:18:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:18:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:19:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:19:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:20:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:20:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:20:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:20:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:21:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:21:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:21:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:21:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:21:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:21:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:22:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:22:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:22:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:22:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:22:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:22:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:23:02 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:23:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:23:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:23:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:23:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:23:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:23:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:23:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:24:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:24:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:24:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:24:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:24:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:25:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:25:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:25:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:25:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:26:02 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:26:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:26:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:26:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:26:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:27:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:27:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:27:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:27:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:28:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:28:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:28:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:28:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:28:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:28:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:28:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:29:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:29:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:29:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:29:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:29:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:30:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:30:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:30:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:30:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:30:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:31:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:31:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:31:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:31:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:31:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:31:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:32:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:32:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:32:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:32:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:32:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:33:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:33:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:33:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:33:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:33:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:34:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:34:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:34:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:34:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:34:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:34:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:34:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:34:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:34:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:02 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:17 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:35:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:36:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:37:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:38:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:39:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:39:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:50:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:50:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:50:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:50:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:50:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 12:50:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 13:24:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 13:24:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 13:24:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 13:24:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 13:25:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:39:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:39:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:40:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:40:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:40:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:40:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:40:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:41:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:41:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:41:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:43:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:43:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:43:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:43:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:43:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:44:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:44:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:44:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:44:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:44:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:45:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:45:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:45:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:45:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:45:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:46:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:46:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:46:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:46:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:46:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:46:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:47:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:47:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:47:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:47:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:47:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:47:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:48:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:48:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:48:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:48:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:48:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:49:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:49:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:49:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:50:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:50:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:50:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:50:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:51:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:51:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:51:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:52:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:52:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:52:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:52:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:52:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:52:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:53:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:53:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:53:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:53:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:53:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:54:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:54:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:54:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:54:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:55:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:55:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:55:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:55:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:56:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:56:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:56:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:56:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:56:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:57:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:57:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:57:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:57:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:58:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:58:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:58:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:58:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:59:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:59:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:59:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 11:59:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:00:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:00:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:00:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:00:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:00:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:00:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:00:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:00:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:01:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:02:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:02:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:02:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:02:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:02:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:02:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:02:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:02:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:02:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:03:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:04:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:05:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:05:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:05:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:05:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:05:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:05:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:05:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:05:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:19:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:19:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:19:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:19:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:19:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Nov 09 12:19:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 10:56:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 10:57:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 10:57:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 10:57:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 10:57:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 10:58:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:40:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:40:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:40:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:40:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:40:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:41:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:41:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:41:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:41:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:42:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:42:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:42:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:42:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:42:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:42:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:42:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:43:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:43:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:43:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:43:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:44:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:44:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:44:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:44:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:44:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:45:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:45:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:45:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:45:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:45:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:46:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:46:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:46:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:46:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:46:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:46:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:47:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:47:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:47:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:47:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:48:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:48:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:48:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:49:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:49:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:49:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:50:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:50:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:50:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:51:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:51:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:51:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:52:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:52:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:52:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:52:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 13:53:00 EST 2025</t>
+    <t>Fri Dec 12 20:24:59 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:25:07 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:25:21 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:25:30 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:25:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:25:46 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:25:54 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:26:03 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:31:13 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:31:28 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:31:41 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:31:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:32:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:32:21 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:32:35 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:32:49 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:33:01 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:33:15 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:33:28 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:33:41 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:33:54 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:34:07 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:34:21 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:34:34 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:34:48 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:35:01 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:35:14 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:35:28 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:35:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:35:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:36:09 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:36:23 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:36:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:36:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:37:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:37:22 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:37:35 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:37:48 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:38:02 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:38:16 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:38:29 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:38:36 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:38:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:38:50 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:38:56 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:02 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:14 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:21 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:32 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:44 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:52 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:39:58 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:40:04 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:40:10 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:40:16 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:40:22 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:40:28 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:40:35 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:40:41 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:40:47 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:40:53 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:06 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:12 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:18 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:24 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:31 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:37 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:44 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:50 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:41:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:05 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:16 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:21 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:27 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:33 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:44 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:49 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:42:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:06 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:11 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:16 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:22 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:28 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:33 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:44 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:50 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:43:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:56:10 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:56:18 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:56:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:56:34 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:56:41 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:56:49 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:06:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:06:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:06:29 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:06:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:06:48 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:06:56 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:07:11 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:07:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:07:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:07:54 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:08:15 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:08:24 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:08:33 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:09:05 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:09:18 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:09:31 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:09:44 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:09:52 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:10:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:10:13 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:10:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:10:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:10:52 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:11:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:11:13 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:11:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:11:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:11:53 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:12:02 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:12:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:12:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:12:58 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:13:10 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:13:23 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:13:40 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:13:58 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:14:17 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:14:25 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:14:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:14:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:15:12 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:15:30 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:15:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:16:03 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:16:09 EST 2025</t>
+  </si>
+  <si>
+    <t>Sun Dec 14 16:16:14 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 17:59:13 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 17:59:25 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 17:59:33 EST 2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3584,24 +994,24 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
-    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3614,14 +1024,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -3654,9 +1064,9 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -3708,7 +1118,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -3760,7 +1170,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3819,21 +1229,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -3850,7 +1260,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -3902,34 +1312,34 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B3BF19-5985-4984-B3CC-B3E33E12951F}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B3BF19-5985-4984-B3CC-B3E33E12951F}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3976,12 +1386,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1101</v>
+        <v>246</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -4002,10 +1412,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -4023,12 +1433,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1102</v>
+        <v>247</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -4049,10 +1459,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -4070,12 +1480,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1103</v>
+        <v>248</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -4096,10 +1506,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -4117,12 +1527,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>1104</v>
+        <v>249</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -4164,12 +1574,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1105</v>
+        <v>250</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -4212,8 +1622,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -4221,27 +1631,27 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2359731-E4E5-4078-88F3-04F82A8C8041}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2359731-E4E5-4078-88F3-04F82A8C8041}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4288,12 +1698,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1145</v>
+        <v>279</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -4314,10 +1724,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -4335,12 +1745,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1146</v>
+        <v>280</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -4361,10 +1771,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -4382,12 +1792,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1147</v>
+        <v>281</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -4408,10 +1818,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -4429,12 +1839,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>1148</v>
+        <v>282</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -4476,12 +1886,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>1149</v>
+        <v>283</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -4524,32 +1934,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC99232A-9CA5-4149-85DE-BA29AA7848F2}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC99232A-9CA5-4149-85DE-BA29AA7848F2}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4596,12 +2006,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1150</v>
+        <v>284</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -4622,10 +2032,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -4643,12 +2053,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1151</v>
+        <v>285</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -4669,10 +2079,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -4690,12 +2100,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1152</v>
+        <v>286</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -4716,10 +2126,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -4737,12 +2147,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>1153</v>
+        <v>287</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -4784,12 +2194,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>1154</v>
+        <v>288</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -4832,34 +2242,34 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F4B3B1-E8F7-45EE-B808-7340C74D1EA9}">
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F4B3B1-E8F7-45EE-B808-7340C74D1EA9}">
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="46.85546875" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="2" width="17.28515625" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="2" width="22.85546875" collapsed="true"/>
-    <col min="16" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="46.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="17.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="22.86328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="16" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="30" r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4906,12 +2316,12 @@
         <v>38</v>
       </c>
     </row>
-    <row ht="30" r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1155</v>
+        <v>289</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -4932,10 +2342,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
@@ -4944,21 +2354,21 @@
         <v>10.5</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="N2" s="2">
         <v>1</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row ht="30" r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>1156</v>
+        <v>290</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -4991,21 +2401,21 @@
         <v>10.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="N3" s="2">
         <v>1</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row ht="30" r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1157</v>
+        <v>291</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -5038,43 +2448,43 @@
         <v>10.5</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="N4" s="2">
         <v>1</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>227</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F3F3A8-CC55-49BE-B541-0DA825F10822}">
-  <dimension ref="A1:AZ34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F3F3A8-CC55-49BE-B541-0DA825F10822}">
+  <dimension ref="A1:AY34"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="12" max="12" style="2" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" style="1" width="9.140625" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="15" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="2" collapsed="1"/>
+    <col min="13" max="13" width="9.1328125" style="1" collapsed="1"/>
+    <col min="14" max="14" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="15" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" ht="45" r="1" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5229,12 +2639,12 @@
         <v>75</v>
       </c>
     </row>
-    <row customFormat="1" ht="45" r="2" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1002</v>
+        <v>153</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -5349,12 +2759,12 @@
       </c>
       <c r="AY2" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="3" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1003</v>
+        <v>154</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -5469,12 +2879,12 @@
       </c>
       <c r="AY3" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="4" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1004</v>
+        <v>155</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -5589,12 +2999,12 @@
       </c>
       <c r="AY4" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="5" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1005</v>
+        <v>156</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -5709,12 +3119,12 @@
       </c>
       <c r="AY5" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="6" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1006</v>
+        <v>157</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -5829,12 +3239,12 @@
       </c>
       <c r="AY6" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="7" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>1007</v>
+        <v>158</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -5949,12 +3359,12 @@
       </c>
       <c r="AY7" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="8" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>1008</v>
+        <v>159</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -6070,12 +3480,12 @@
       </c>
       <c r="AY8" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="9" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>1009</v>
+        <v>160</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -6191,12 +3601,12 @@
       </c>
       <c r="AY9" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="10" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>1010</v>
+        <v>161</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -6312,12 +3722,12 @@
       </c>
       <c r="AY10" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="11" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>1011</v>
+        <v>162</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -6432,12 +3842,12 @@
       </c>
       <c r="AY11" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="12" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>1012</v>
+        <v>163</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
@@ -6552,12 +3962,12 @@
       </c>
       <c r="AY12" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="13" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>1013</v>
+        <v>164</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>20</v>
@@ -6672,12 +4082,12 @@
       </c>
       <c r="AY13" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="14" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>1014</v>
+        <v>165</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -6792,12 +4202,12 @@
       </c>
       <c r="AY14" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="15" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>1015</v>
+        <v>166</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>20</v>
@@ -6912,12 +4322,12 @@
       </c>
       <c r="AY15" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="16" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>1016</v>
+        <v>167</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
@@ -7032,12 +4442,12 @@
       </c>
       <c r="AY16" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="17" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>1017</v>
+        <v>168</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>20</v>
@@ -7152,12 +4562,12 @@
       </c>
       <c r="AY17" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="18" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>1018</v>
+        <v>169</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>20</v>
@@ -7272,12 +4682,12 @@
       </c>
       <c r="AY18" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="19" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>1019</v>
+        <v>170</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>20</v>
@@ -7392,12 +4802,12 @@
       </c>
       <c r="AY19" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="20" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>1020</v>
+        <v>171</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
@@ -7512,12 +4922,12 @@
       </c>
       <c r="AY20" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="21" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>1021</v>
+        <v>172</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>20</v>
@@ -7632,12 +5042,12 @@
       </c>
       <c r="AY21" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="22" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>1022</v>
+        <v>173</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
@@ -7752,12 +5162,12 @@
       </c>
       <c r="AY22" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="23" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>1023</v>
+        <v>174</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -7872,12 +5282,12 @@
       </c>
       <c r="AY23" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="24" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>1024</v>
+        <v>175</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>20</v>
@@ -7992,12 +5402,12 @@
       </c>
       <c r="AY24" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="25" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>1025</v>
+        <v>176</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -8112,12 +5522,12 @@
       </c>
       <c r="AY25" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="26" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>1026</v>
+        <v>177</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -8232,12 +5642,12 @@
       </c>
       <c r="AY26" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="27" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>1027</v>
+        <v>178</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
@@ -8352,12 +5762,12 @@
       </c>
       <c r="AY27" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="28" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>1028</v>
+        <v>179</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>20</v>
@@ -8472,12 +5882,12 @@
       </c>
       <c r="AY28" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="29" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>1029</v>
+        <v>180</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -8592,12 +6002,12 @@
       </c>
       <c r="AY29" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="30" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>1030</v>
+        <v>181</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
@@ -8712,12 +6122,12 @@
       </c>
       <c r="AY30" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="31" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>1031</v>
+        <v>182</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>20</v>
@@ -8832,12 +6242,12 @@
       </c>
       <c r="AY31" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="32" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>1032</v>
+        <v>183</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>20</v>
@@ -8952,12 +6362,12 @@
       </c>
       <c r="AY32" s="4"/>
     </row>
-    <row customFormat="1" ht="45" r="33" s="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>1033</v>
+        <v>184</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>20</v>
@@ -9072,37 +6482,37 @@
       </c>
       <c r="AY33" s="4"/>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.45">
       <c r="L34" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EF3280-CA4E-46F2-B2B8-2F43A765033A}">
-  <dimension ref="A1:W34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EF3280-CA4E-46F2-B2B8-2F43A765033A}">
+  <dimension ref="A1:V34"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="12" max="12" style="2" width="9.140625" collapsed="true"/>
-    <col min="13" max="14" customWidth="true" style="2" width="11.28515625" collapsed="true"/>
-    <col min="15" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="2" collapsed="1"/>
+    <col min="13" max="14" width="11.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="15" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" ht="30" r="1" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9170,12 +6580,12 @@
         <v>55</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="2" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1034</v>
+        <v>185</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -9235,12 +6645,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="3" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1035</v>
+        <v>186</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -9300,12 +6710,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="4" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1036</v>
+        <v>187</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -9365,12 +6775,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="5" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1037</v>
+        <v>188</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -9430,12 +6840,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="6" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1038</v>
+        <v>189</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -9495,12 +6905,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="7" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>1039</v>
+        <v>190</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -9560,12 +6970,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="8" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>1040</v>
+        <v>191</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9626,12 +7036,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="9" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>1041</v>
+        <v>192</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -9692,12 +7102,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="10" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>1042</v>
+        <v>193</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -9758,12 +7168,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="11" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>1043</v>
+        <v>194</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -9823,12 +7233,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="12" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>1044</v>
+        <v>195</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
@@ -9888,12 +7298,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="13" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>1045</v>
+        <v>196</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>20</v>
@@ -9953,12 +7363,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="14" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>1046</v>
+        <v>197</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -10018,12 +7428,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="15" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>1047</v>
+        <v>198</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>20</v>
@@ -10083,12 +7493,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="16" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>1048</v>
+        <v>199</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
@@ -10148,12 +7558,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="17" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>1049</v>
+        <v>200</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>20</v>
@@ -10213,12 +7623,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="18" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>1050</v>
+        <v>201</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>20</v>
@@ -10278,12 +7688,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="19" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>1051</v>
+        <v>202</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>20</v>
@@ -10343,12 +7753,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="20" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>1052</v>
+        <v>203</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
@@ -10408,12 +7818,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="21" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>1053</v>
+        <v>204</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>20</v>
@@ -10473,12 +7883,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="22" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>1054</v>
+        <v>205</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
@@ -10538,12 +7948,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="23" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>1055</v>
+        <v>206</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -10603,12 +8013,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="24" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>1056</v>
+        <v>207</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>20</v>
@@ -10668,12 +8078,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="25" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>1057</v>
+        <v>208</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -10733,12 +8143,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="26" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>1058</v>
+        <v>209</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -10798,12 +8208,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="27" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>1059</v>
+        <v>210</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
@@ -10863,12 +8273,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="28" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>1060</v>
+        <v>211</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>20</v>
@@ -10928,12 +8338,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="29" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>1061</v>
+        <v>212</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -10993,12 +8403,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="30" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>1062</v>
+        <v>213</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
@@ -11058,12 +8468,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="31" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>1063</v>
+        <v>214</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>20</v>
@@ -11123,12 +8533,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="32" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>1064</v>
+        <v>215</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>20</v>
@@ -11188,12 +8598,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="33" s="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>1065</v>
+        <v>216</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>20</v>
@@ -11253,34 +8663,34 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.45">
       <c r="L34" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA243B-4AA6-4B80-8D83-694CE3832665}">
-  <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA243B-4AA6-4B80-8D83-694CE3832665}">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="11" max="12" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="13" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11321,12 +8731,12 @@
         <v>5</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="2" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1066</v>
+        <v>217</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -11359,12 +8769,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="3" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1067</v>
+        <v>218</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -11397,12 +8807,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="4" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1068</v>
+        <v>219</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -11436,12 +8846,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="5" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1069</v>
+        <v>220</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -11474,12 +8884,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="6" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1070</v>
+        <v>221</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -11512,12 +8922,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>1071</v>
+        <v>222</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -11550,12 +8960,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>1072</v>
+        <v>223</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -11588,12 +8998,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>1073</v>
+        <v>224</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -11626,34 +9036,34 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="I10" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9035B600-1AE4-4F39-B9B0-C3B647778074}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9035B600-1AE4-4F39-B9B0-C3B647778074}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="11" max="12" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="13" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11691,12 +9101,12 @@
         <v>124</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="2" s="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1074</v>
+        <v>225</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -11726,12 +9136,12 @@
         <v>125</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="3" s="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1075</v>
+        <v>226</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -11761,12 +9171,12 @@
         <v>125</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="4" s="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1076</v>
+        <v>227</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -11797,12 +9207,12 @@
         <v>125</v>
       </c>
     </row>
-    <row customFormat="1" r="5" s="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1077</v>
+        <v>228</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -11832,12 +9242,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1078</v>
+        <v>229</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -11867,12 +9277,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>1079</v>
+        <v>230</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -11902,12 +9312,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>1080</v>
+        <v>231</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -11937,34 +9347,34 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="I9" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D985158-3685-4E06-8AAF-5C6291ED2A2E}">
-  <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D985158-3685-4E06-8AAF-5C6291ED2A2E}">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="11" max="12" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="13" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12005,12 +9415,12 @@
         <v>5</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="2" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1081</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -12043,12 +9453,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="3" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1082</v>
+        <v>233</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -12081,12 +9491,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" ht="30" r="4" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1083</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -12120,12 +9530,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="5" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1084</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -12158,12 +9568,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="6" s="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1085</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -12196,12 +9606,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>1086</v>
+        <v>237</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -12234,12 +9644,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>1087</v>
+        <v>238</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -12272,12 +9682,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>1088</v>
+        <v>239</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -12310,36 +9720,36 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="I10" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A3FE28-6D3A-468C-B453-4E8625D9142D}">
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A3FE28-6D3A-468C-B453-4E8625D9142D}">
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="24.28515625" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="24.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12386,12 +9796,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1092</v>
+        <v>243</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
@@ -12424,12 +9834,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1093</v>
+        <v>244</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>129</v>
@@ -12462,12 +9872,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1094</v>
+        <v>245</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>129</v>
@@ -12501,32 +9911,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C12825-4D21-4476-8848-6E435EC04842}">
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C12825-4D21-4476-8848-6E435EC04842}">
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="30.5703125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="30.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12573,12 +9983,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1089</v>
+        <v>240</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
@@ -12611,12 +10021,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1090</v>
+        <v>241</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>129</v>
@@ -12649,12 +10059,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1091</v>
+        <v>242</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>129</v>
@@ -12688,32 +10098,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77641590-759F-4E9F-886E-0EE016894C97}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77641590-759F-4E9F-886E-0EE016894C97}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12760,12 +10170,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1106</v>
+        <v>251</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -12786,10 +10196,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -12807,12 +10217,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1107</v>
+        <v>252</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -12833,10 +10243,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -12854,12 +10264,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1108</v>
+        <v>253</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -12880,10 +10290,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -12901,12 +10311,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1109</v>
+        <v>254</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -12948,12 +10358,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>1110</v>
+        <v>255</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -12996,7 +10406,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -13004,25 +10414,25 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DCF843-7CC4-48A5-8072-F1A801B90CE0}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DCF843-7CC4-48A5-8072-F1A801B90CE0}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="21.0" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="21.42578125" collapsed="true"/>
-    <col min="10" max="10" style="2" width="9.140625" collapsed="true"/>
-    <col min="11" max="11" style="1" width="9.140625" collapsed="true"/>
-    <col min="12" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="21" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="21.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="9.1328125" style="2" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="1" collapsed="1"/>
+    <col min="12" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13036,7 +10446,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>283</v>
+        <v>141</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>111</v>
@@ -13057,18 +10467,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>143</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>284</v>
+        <v>142</v>
       </c>
       <c r="F2" s="2">
         <v>234</v>
@@ -13090,32 +10500,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F862F746-9284-4D5F-8449-DC04488EA2C6}">
-  <dimension ref="A1:P7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F862F746-9284-4D5F-8449-DC04488EA2C6}">
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="18.5703125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="18.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13162,12 +10572,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1111</v>
+        <v>256</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -13188,10 +10598,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -13209,12 +10619,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1112</v>
+        <v>257</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -13235,10 +10645,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -13256,12 +10666,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1113</v>
+        <v>258</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -13282,10 +10692,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -13303,12 +10713,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1114</v>
+        <v>292</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -13350,12 +10760,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1115</v>
+        <v>293</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -13397,15 +10807,15 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>1116</v>
+        <v>294</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>276</v>
+        <v>136</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>25</v>
@@ -13414,19 +10824,19 @@
         <v>591</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>277</v>
+        <v>137</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>278</v>
+        <v>138</v>
       </c>
       <c r="H7" s="2">
         <v>4494</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>279</v>
+        <v>139</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>17</v>
@@ -13435,7 +10845,7 @@
         <v>10.5</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>286</v>
+        <v>144</v>
       </c>
       <c r="N7" s="2">
         <v>12</v>
@@ -13445,32 +10855,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD14A431-43B3-4E34-B368-8DDA4A423BE8}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD14A431-43B3-4E34-B368-8DDA4A423BE8}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13517,12 +10927,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1117</v>
+        <v>259</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -13543,10 +10953,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -13564,12 +10974,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1118</v>
+        <v>260</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -13590,10 +11000,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -13611,12 +11021,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1119</v>
+        <v>261</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -13637,10 +11047,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -13658,12 +11068,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>1120</v>
+        <v>262</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -13705,12 +11115,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>1121</v>
+        <v>263</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -13743,7 +11153,7 @@
         <v>10.5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>286</v>
+        <v>144</v>
       </c>
       <c r="N6" s="2">
         <v>12</v>
@@ -13753,32 +11163,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDEE7-E2F6-498C-8E90-D24ED0C44AC2}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDEE7-E2F6-498C-8E90-D24ED0C44AC2}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13825,12 +11235,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1122</v>
+        <v>264</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -13851,10 +11261,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -13872,12 +11282,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1123</v>
+        <v>265</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -13898,10 +11308,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -13919,12 +11329,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1124</v>
+        <v>266</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -13945,10 +11355,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -13966,12 +11376,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>1125</v>
+        <v>267</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -14013,12 +11423,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>1126</v>
+        <v>268</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -14061,32 +11471,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C85066F-A70F-4EC6-96A2-3B11D71E8332}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C85066F-A70F-4EC6-96A2-3B11D71E8332}">
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="46.85546875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="46.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14127,12 +11537,12 @@
         <v>35</v>
       </c>
     </row>
-    <row ht="45" r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1127</v>
+        <v>145</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -14153,10 +11563,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
@@ -14165,15 +11575,15 @@
         <v>10.5</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row ht="45" r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1128</v>
+        <v>146</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -14206,15 +11616,15 @@
         <v>10.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row ht="45" r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1129</v>
+        <v>147</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -14247,36 +11657,36 @@
         <v>10.5</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA94AF-A176-4725-8452-BA8E3503AAAB}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA94AF-A176-4725-8452-BA8E3503AAAB}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14323,12 +11733,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1130</v>
+        <v>148</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -14349,10 +11759,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -14370,12 +11780,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1131</v>
+        <v>149</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -14396,10 +11806,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -14417,12 +11827,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1132</v>
+        <v>150</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -14443,10 +11853,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -14464,12 +11874,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1133</v>
+        <v>151</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -14511,12 +11921,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1134</v>
+        <v>152</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -14559,32 +11969,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407A61CA-7BCD-4622-83EC-6EE78F45F1F1}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407A61CA-7BCD-4622-83EC-6EE78F45F1F1}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14631,12 +12041,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1135</v>
+        <v>269</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -14657,10 +12067,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -14678,12 +12088,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1136</v>
+        <v>270</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -14704,10 +12114,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -14725,12 +12135,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1137</v>
+        <v>271</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -14751,10 +12161,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -14772,12 +12182,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>1138</v>
+        <v>272</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -14819,12 +12229,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>1139</v>
+        <v>273</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -14867,32 +12277,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846A7054-8630-44CB-A36C-72BF4E3BB15C}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846A7054-8630-44CB-A36C-72BF4E3BB15C}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.140625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.140625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.42578125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.140625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.140625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.28515625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.140625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.7109375" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14939,12 +12349,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1140</v>
+        <v>274</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -14965,10 +12375,10 @@
         <v>1773</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
@@ -14986,12 +12396,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1141</v>
+        <v>275</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -15012,10 +12422,10 @@
         <v>1773</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
@@ -15033,12 +12443,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1142</v>
+        <v>276</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -15059,10 +12469,10 @@
         <v>1773</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -15080,12 +12490,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>1143</v>
+        <v>277</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -15127,12 +12537,12 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>1144</v>
+        <v>278</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -15175,6 +12585,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/VLinkSmokeData.xlsx
+++ b/KatalonData/VLinkSmokeData.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B75DAD-2D41-47E3-A99D-5900C500CD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{78B75DAD-2D41-47E3-A99D-5900C500CD8A}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="3083" windowWidth="21600" windowHeight="11392" tabRatio="887" activeTab="2" xr2:uid="{D3A86137-2393-48B3-A2A1-24E657E7CF34}"/>
+    <workbookView activeTab="2" tabRatio="887" windowHeight="11392" windowWidth="21600" xWindow="3960" xr2:uid="{D3A86137-2393-48B3-A2A1-24E657E7CF34}" yWindow="3083"/>
   </bookViews>
   <sheets>
-    <sheet name="Auth" sheetId="1" r:id="rId1"/>
-    <sheet name="AuthCapture" sheetId="2" r:id="rId2"/>
-    <sheet name="Sale" sheetId="3" r:id="rId3"/>
-    <sheet name="Sale-Void" sheetId="4" r:id="rId4"/>
-    <sheet name="Sale-Credit" sheetId="5" r:id="rId5"/>
-    <sheet name="Sale-Unencrypted" sheetId="6" r:id="rId6"/>
-    <sheet name="Sale-ZeroDollar" sheetId="7" r:id="rId7"/>
-    <sheet name="Sale-Void-NoTranxID" sheetId="8" r:id="rId8"/>
-    <sheet name="Sale-Credit-Void" sheetId="9" r:id="rId9"/>
-    <sheet name="Auth-Cap-Void" sheetId="10" r:id="rId10"/>
-    <sheet name="Auth-Cap-Credit" sheetId="11" r:id="rId11"/>
-    <sheet name="Sale-Encrypted" sheetId="12" r:id="rId12"/>
-    <sheet name="Sale-MRF" sheetId="13" r:id="rId13"/>
-    <sheet name="Auth-MRF" sheetId="14" r:id="rId14"/>
-    <sheet name="Cap-MRF" sheetId="15" r:id="rId15"/>
-    <sheet name="Void-MRF" sheetId="16" r:id="rId16"/>
-    <sheet name="Credit-MRF" sheetId="17" r:id="rId17"/>
-    <sheet name="Sale-CardNotAccepted" sheetId="18" r:id="rId18"/>
-    <sheet name="Auth-CardNotAccepted" sheetId="19" r:id="rId19"/>
-    <sheet name="CreditClient" sheetId="20" r:id="rId20"/>
+    <sheet name="Auth" r:id="rId1" sheetId="1"/>
+    <sheet name="AuthCapture" r:id="rId2" sheetId="2"/>
+    <sheet name="Sale" r:id="rId3" sheetId="3"/>
+    <sheet name="Sale-Void" r:id="rId4" sheetId="4"/>
+    <sheet name="Sale-Credit" r:id="rId5" sheetId="5"/>
+    <sheet name="Sale-Unencrypted" r:id="rId6" sheetId="6"/>
+    <sheet name="Sale-ZeroDollar" r:id="rId7" sheetId="7"/>
+    <sheet name="Sale-Void-NoTranxID" r:id="rId8" sheetId="8"/>
+    <sheet name="Sale-Credit-Void" r:id="rId9" sheetId="9"/>
+    <sheet name="Auth-Cap-Void" r:id="rId10" sheetId="10"/>
+    <sheet name="Auth-Cap-Credit" r:id="rId11" sheetId="11"/>
+    <sheet name="Sale-Encrypted" r:id="rId12" sheetId="12"/>
+    <sheet name="Sale-MRF" r:id="rId13" sheetId="13"/>
+    <sheet name="Auth-MRF" r:id="rId14" sheetId="14"/>
+    <sheet name="Cap-MRF" r:id="rId15" sheetId="15"/>
+    <sheet name="Void-MRF" r:id="rId16" sheetId="16"/>
+    <sheet name="Credit-MRF" r:id="rId17" sheetId="17"/>
+    <sheet name="Sale-CardNotAccepted" r:id="rId18" sheetId="18"/>
+    <sheet name="Auth-CardNotAccepted" r:id="rId19" sheetId="19"/>
+    <sheet name="CreditClient" r:id="rId20" sheetId="20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3662" uniqueCount="446">
   <si>
     <t>Result</t>
   </si>
@@ -940,12 +940,466 @@
   </si>
   <si>
     <t>Tue Dec 16 17:59:33 EST 2025</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:24:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:24:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:24:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:24:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:25:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:25:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:25:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:25:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:26:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:26:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:27:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:27:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:28:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:28:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:28:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:28:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:28:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:28:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:28:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:29:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:29:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:29:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:29:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:30:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:30:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:30:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:30:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:30:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:31:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:31:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:31:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:31:22 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:31:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:31:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:31:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:31:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:32:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:32:23 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:32:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:33:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:33:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:33:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:33:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:34:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:34:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:34:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:35:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:35:33 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:35:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:36:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:36:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:36:42 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:37:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:37:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:37:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:37:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:37:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:37:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:38:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:38:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:38:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:38:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:38:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:39:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:39:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:39:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:39:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:40:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:40:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:40:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:40:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:40:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:41:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:41:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:41:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:41:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:42:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:42:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:42:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:42:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:42:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:43:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:43:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:43:38 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:43:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:44:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:44:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:44:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:44:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:45:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:23 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:46:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:47:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:47:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:47:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:47:23 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:47:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:47:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:47:42 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:47:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:47:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:48:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:09 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:49:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:03:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:03:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:03:42 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:03:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:03:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:04:06 EST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -994,24 +1448,24 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1028,10 +1482,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1066,7 +1520,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1118,7 +1572,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1229,21 +1683,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1260,7 +1714,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1312,31 +1766,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B3BF19-5985-4984-B3CC-B3E33E12951F}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B3BF19-5985-4984-B3CC-B3E33E12951F}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1391,7 +1845,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -1438,7 +1892,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -1485,7 +1939,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -1529,10 +1983,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1579,7 +2033,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -1622,8 +2076,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1631,24 +2085,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2359731-E4E5-4078-88F3-04F82A8C8041}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2359731-E4E5-4078-88F3-04F82A8C8041}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1703,7 +2157,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>279</v>
+        <v>340</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -1750,7 +2204,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>341</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -1797,7 +2251,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -1841,10 +2295,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1888,10 +2342,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -1934,29 +2388,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC99232A-9CA5-4149-85DE-BA29AA7848F2}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC99232A-9CA5-4149-85DE-BA29AA7848F2}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -2011,7 +2465,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>345</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -2058,7 +2512,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -2105,7 +2559,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>286</v>
+        <v>347</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -2149,10 +2603,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>287</v>
+        <v>348</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -2196,10 +2650,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -2242,31 +2696,31 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F4B3B1-E8F7-45EE-B808-7340C74D1EA9}">
-  <dimension ref="A1:O4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F4B3B1-E8F7-45EE-B808-7340C74D1EA9}">
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="46.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="17.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="22.86328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="16" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="46.86328125" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="2" width="17.265625" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="2" width="22.86328125" collapsed="true"/>
+    <col min="16" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -2316,12 +2770,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
+    <row ht="28.5" r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -2363,12 +2817,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
+    <row ht="28.5" r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -2410,12 +2864,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
+    <row ht="28.5" r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -2458,33 +2912,33 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F3F3A8-CC55-49BE-B541-0DA825F10822}">
-  <dimension ref="A1:AY34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F3F3A8-CC55-49BE-B541-0DA825F10822}">
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="2" collapsed="1"/>
-    <col min="13" max="13" width="9.1328125" style="1" collapsed="1"/>
-    <col min="14" max="14" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="12" max="12" style="2" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" style="1" width="9.1328125" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="15" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="1" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2639,12 +3093,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="2" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>353</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -2759,12 +3213,12 @@
       </c>
       <c r="AY2" s="4"/>
     </row>
-    <row r="3" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="3" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>354</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -2879,12 +3333,12 @@
       </c>
       <c r="AY3" s="4"/>
     </row>
-    <row r="4" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="4" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>355</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -2999,12 +3453,12 @@
       </c>
       <c r="AY4" s="4"/>
     </row>
-    <row r="5" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="5" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>356</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -3119,12 +3573,12 @@
       </c>
       <c r="AY5" s="4"/>
     </row>
-    <row r="6" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="6" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>357</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -3239,12 +3693,12 @@
       </c>
       <c r="AY6" s="4"/>
     </row>
-    <row r="7" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="7" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>358</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -3359,12 +3813,12 @@
       </c>
       <c r="AY7" s="4"/>
     </row>
-    <row r="8" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="8" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>359</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -3480,12 +3934,12 @@
       </c>
       <c r="AY8" s="4"/>
     </row>
-    <row r="9" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="9" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -3601,12 +4055,12 @@
       </c>
       <c r="AY9" s="4"/>
     </row>
-    <row r="10" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="10" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>161</v>
+        <v>361</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -3722,12 +4176,12 @@
       </c>
       <c r="AY10" s="4"/>
     </row>
-    <row r="11" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="11" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -3842,12 +4296,12 @@
       </c>
       <c r="AY11" s="4"/>
     </row>
-    <row r="12" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="12" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
@@ -3962,12 +4416,12 @@
       </c>
       <c r="AY12" s="4"/>
     </row>
-    <row r="13" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="13" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>20</v>
@@ -4082,12 +4536,12 @@
       </c>
       <c r="AY13" s="4"/>
     </row>
-    <row r="14" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="14" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -4202,12 +4656,12 @@
       </c>
       <c r="AY14" s="4"/>
     </row>
-    <row r="15" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="15" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>366</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>20</v>
@@ -4322,12 +4776,12 @@
       </c>
       <c r="AY15" s="4"/>
     </row>
-    <row r="16" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="16" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>167</v>
+        <v>367</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
@@ -4442,12 +4896,12 @@
       </c>
       <c r="AY16" s="4"/>
     </row>
-    <row r="17" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="17" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>168</v>
+        <v>368</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>20</v>
@@ -4562,12 +5016,12 @@
       </c>
       <c r="AY17" s="4"/>
     </row>
-    <row r="18" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="18" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>169</v>
+        <v>369</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>20</v>
@@ -4682,12 +5136,12 @@
       </c>
       <c r="AY18" s="4"/>
     </row>
-    <row r="19" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="19" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>170</v>
+        <v>370</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>20</v>
@@ -4802,12 +5256,12 @@
       </c>
       <c r="AY19" s="4"/>
     </row>
-    <row r="20" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="20" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>171</v>
+        <v>371</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
@@ -4922,12 +5376,12 @@
       </c>
       <c r="AY20" s="4"/>
     </row>
-    <row r="21" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="21" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>372</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>20</v>
@@ -5042,12 +5496,12 @@
       </c>
       <c r="AY21" s="4"/>
     </row>
-    <row r="22" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="22" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>173</v>
+        <v>373</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
@@ -5162,12 +5616,12 @@
       </c>
       <c r="AY22" s="4"/>
     </row>
-    <row r="23" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="23" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>374</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -5282,12 +5736,12 @@
       </c>
       <c r="AY23" s="4"/>
     </row>
-    <row r="24" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="24" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>175</v>
+        <v>375</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>20</v>
@@ -5402,12 +5856,12 @@
       </c>
       <c r="AY24" s="4"/>
     </row>
-    <row r="25" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="25" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>176</v>
+        <v>376</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -5522,12 +5976,12 @@
       </c>
       <c r="AY25" s="4"/>
     </row>
-    <row r="26" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="26" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>177</v>
+        <v>377</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -5642,12 +6096,12 @@
       </c>
       <c r="AY26" s="4"/>
     </row>
-    <row r="27" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="27" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>178</v>
+        <v>378</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
@@ -5762,12 +6216,12 @@
       </c>
       <c r="AY27" s="4"/>
     </row>
-    <row r="28" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="28" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>179</v>
+        <v>379</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>20</v>
@@ -5882,12 +6336,12 @@
       </c>
       <c r="AY28" s="4"/>
     </row>
-    <row r="29" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="29" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -6002,12 +6456,12 @@
       </c>
       <c r="AY29" s="4"/>
     </row>
-    <row r="30" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="30" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>181</v>
+        <v>381</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
@@ -6122,12 +6576,12 @@
       </c>
       <c r="AY30" s="4"/>
     </row>
-    <row r="31" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="31" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>182</v>
+        <v>382</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>20</v>
@@ -6242,12 +6696,12 @@
       </c>
       <c r="AY31" s="4"/>
     </row>
-    <row r="32" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="32" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>183</v>
+        <v>383</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>20</v>
@@ -6362,12 +6816,12 @@
       </c>
       <c r="AY32" s="4"/>
     </row>
-    <row r="33" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="33" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>184</v>
+        <v>384</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>20</v>
@@ -6486,33 +6940,33 @@
       <c r="L34" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EF3280-CA4E-46F2-B2B8-2F43A765033A}">
-  <dimension ref="A1:V34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EF3280-CA4E-46F2-B2B8-2F43A765033A}">
+  <dimension ref="A1:W34"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="2" collapsed="1"/>
-    <col min="13" max="14" width="11.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="15" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="12" max="12" style="2" width="9.1328125" collapsed="true"/>
+    <col min="13" max="14" customWidth="true" style="2" width="11.265625" collapsed="true"/>
+    <col min="15" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="1" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6580,12 +7034,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -6645,12 +7099,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>386</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -6710,12 +7164,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="4" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>387</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -6775,12 +7229,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="5" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>388</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -6840,12 +7294,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="6" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>389</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -6905,12 +7359,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="7" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -6970,12 +7424,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="8" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>391</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -7036,12 +7490,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="9" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>392</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -7102,12 +7556,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="10" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -7168,12 +7622,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="11" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>194</v>
+        <v>394</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -7233,12 +7687,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="12" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>195</v>
+        <v>395</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
@@ -7298,12 +7752,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="13" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>196</v>
+        <v>396</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>20</v>
@@ -7363,12 +7817,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="14" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>397</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -7428,12 +7882,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="15" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>398</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>20</v>
@@ -7493,12 +7947,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="16" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>399</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
@@ -7558,12 +8012,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="17" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>20</v>
@@ -7623,12 +8077,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="18" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>20</v>
@@ -7688,12 +8142,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="19" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>202</v>
+        <v>402</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>20</v>
@@ -7753,12 +8207,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="20" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>203</v>
+        <v>403</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
@@ -7818,12 +8272,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="21" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>204</v>
+        <v>404</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>20</v>
@@ -7883,12 +8337,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="22" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>205</v>
+        <v>405</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
@@ -7948,12 +8402,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="23" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>206</v>
+        <v>406</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -8013,12 +8467,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="24" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>207</v>
+        <v>407</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>20</v>
@@ -8078,12 +8532,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="25" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>208</v>
+        <v>408</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -8143,12 +8597,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="26" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>209</v>
+        <v>409</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -8208,12 +8662,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="27" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>210</v>
+        <v>410</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
@@ -8273,12 +8727,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="28" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>211</v>
+        <v>411</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>20</v>
@@ -8338,12 +8792,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="29" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>212</v>
+        <v>412</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -8403,12 +8857,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="30" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>213</v>
+        <v>413</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
@@ -8468,12 +8922,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="31" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>214</v>
+        <v>414</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>20</v>
@@ -8533,12 +8987,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="32" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>415</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>20</v>
@@ -8598,12 +9052,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="33" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>216</v>
+        <v>416</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>20</v>
@@ -8667,30 +9121,30 @@
       <c r="L34" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA243B-4AA6-4B80-8D83-694CE3832665}">
-  <dimension ref="A1:M10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA243B-4AA6-4B80-8D83-694CE3832665}">
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="12" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="13" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="1" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8731,12 +9185,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>417</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -8769,12 +9223,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>418</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -8807,12 +9261,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="4" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>419</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -8846,12 +9300,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="5" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -8884,12 +9338,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="6" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>421</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -8927,7 +9381,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>422</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -8965,7 +9419,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>423</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9003,7 +9457,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>224</v>
+        <v>424</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -9040,30 +9494,30 @@
       <c r="I10" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9035B600-1AE4-4F39-B9B0-C3B647778074}">
-  <dimension ref="A1:L9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9035B600-1AE4-4F39-B9B0-C3B647778074}">
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="12" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="13" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="1" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9101,12 +9555,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -9136,12 +9590,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>426</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -9171,12 +9625,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="4" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>427</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -9207,12 +9661,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="5" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>428</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -9247,7 +9701,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>229</v>
+        <v>429</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -9282,7 +9736,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>230</v>
+        <v>430</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -9317,7 +9771,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>431</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9351,30 +9805,30 @@
       <c r="I9" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D985158-3685-4E06-8AAF-5C6291ED2A2E}">
-  <dimension ref="A1:M10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D985158-3685-4E06-8AAF-5C6291ED2A2E}">
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="12" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="13" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="1" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9415,12 +9869,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>432</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -9453,12 +9907,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>433</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -9491,12 +9945,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="4" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>434</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -9530,12 +9984,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="5" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>435</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -9568,12 +10022,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="6" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>436</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -9611,7 +10065,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>437</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -9649,7 +10103,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>438</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9687,7 +10141,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>239</v>
+        <v>439</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -9724,29 +10178,29 @@
       <c r="I10" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A3FE28-6D3A-468C-B453-4E8625D9142D}">
-  <dimension ref="A1:O4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A3FE28-6D3A-468C-B453-4E8625D9142D}">
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="24.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="24.265625" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -9801,7 +10255,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>443</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
@@ -9839,7 +10293,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>444</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>129</v>
@@ -9877,7 +10331,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>445</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>129</v>
@@ -9911,29 +10365,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C12825-4D21-4476-8848-6E435EC04842}">
-  <dimension ref="A1:O4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C12825-4D21-4476-8848-6E435EC04842}">
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="30.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="30.59765625" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -9988,7 +10442,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
@@ -10026,7 +10480,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>441</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>129</v>
@@ -10064,7 +10518,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>442</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>129</v>
@@ -10098,29 +10552,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77641590-759F-4E9F-886E-0EE016894C97}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77641590-759F-4E9F-886E-0EE016894C97}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -10175,7 +10629,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>301</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -10222,7 +10676,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>302</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -10269,7 +10723,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -10316,7 +10770,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -10360,10 +10814,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -10406,7 +10860,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -10414,22 +10868,22 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DCF843-7CC4-48A5-8072-F1A801B90CE0}">
-  <dimension ref="A1:K2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DCF843-7CC4-48A5-8072-F1A801B90CE0}">
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="21" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="21.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="9.1328125" style="2" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="1" collapsed="1"/>
-    <col min="12" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="21.0" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="21.3984375" collapsed="true"/>
+    <col min="10" max="10" style="2" width="9.1328125" collapsed="true"/>
+    <col min="11" max="11" style="1" width="9.1328125" collapsed="true"/>
+    <col min="12" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
@@ -10500,29 +10954,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F862F746-9284-4D5F-8449-DC04488EA2C6}">
-  <dimension ref="A1:O7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F862F746-9284-4D5F-8449-DC04488EA2C6}">
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="18.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="18.59765625" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -10577,7 +11031,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>306</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -10624,7 +11078,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -10671,7 +11125,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -10718,7 +11172,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -10765,7 +11219,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -10809,10 +11263,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>136</v>
@@ -10855,29 +11309,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD14A431-43B3-4E34-B368-8DDA4A423BE8}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD14A431-43B3-4E34-B368-8DDA4A423BE8}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -10932,7 +11386,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -10979,7 +11433,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>260</v>
+        <v>313</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -11026,7 +11480,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -11070,10 +11524,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>315</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -11117,10 +11571,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -11163,29 +11617,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDEE7-E2F6-498C-8E90-D24ED0C44AC2}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDEE7-E2F6-498C-8E90-D24ED0C44AC2}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -11240,7 +11694,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>317</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -11287,7 +11741,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -11334,7 +11788,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -11378,10 +11832,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>267</v>
+        <v>320</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -11425,10 +11879,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -11471,29 +11925,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C85066F-A70F-4EC6-96A2-3B11D71E8332}">
-  <dimension ref="A1:M4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C85066F-A70F-4EC6-96A2-3B11D71E8332}">
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="46.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="46.86328125" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -11537,12 +11991,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
+    <row ht="42.75" r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>322</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -11578,12 +12032,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
+    <row ht="42.75" r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>323</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -11619,12 +12073,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
+    <row ht="42.75" r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>324</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -11661,29 +12115,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA94AF-A176-4725-8452-BA8E3503AAAB}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA94AF-A176-4725-8452-BA8E3503AAAB}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -11738,7 +12192,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>325</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -11785,7 +12239,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>326</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -11832,7 +12286,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>327</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -11879,7 +12333,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>328</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -11926,7 +12380,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>329</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -11969,29 +12423,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407A61CA-7BCD-4622-83EC-6EE78F45F1F1}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407A61CA-7BCD-4622-83EC-6EE78F45F1F1}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -12046,7 +12500,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -12093,7 +12547,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -12140,7 +12594,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -12184,10 +12638,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>333</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -12231,10 +12685,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>273</v>
+        <v>334</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -12277,29 +12731,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846A7054-8630-44CB-A36C-72BF4E3BB15C}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846A7054-8630-44CB-A36C-72BF4E3BB15C}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -12354,7 +12808,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>274</v>
+        <v>335</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -12401,7 +12855,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>336</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -12448,7 +12902,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -12492,10 +12946,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>277</v>
+        <v>338</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -12539,10 +12993,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -12585,6 +13039,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/KatalonData/VLinkSmokeData.xlsx
+++ b/KatalonData/VLinkSmokeData.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{78B75DAD-2D41-47E3-A99D-5900C500CD8A}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B75DAD-2D41-47E3-A99D-5900C500CD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="2" tabRatio="887" windowHeight="11392" windowWidth="21600" xWindow="3960" xr2:uid="{D3A86137-2393-48B3-A2A1-24E657E7CF34}" yWindow="3083"/>
+    <workbookView xWindow="48312" yWindow="5352" windowWidth="26556" windowHeight="12228" tabRatio="887" activeTab="2" xr2:uid="{D3A86137-2393-48B3-A2A1-24E657E7CF34}"/>
   </bookViews>
   <sheets>
-    <sheet name="Auth" r:id="rId1" sheetId="1"/>
-    <sheet name="AuthCapture" r:id="rId2" sheetId="2"/>
-    <sheet name="Sale" r:id="rId3" sheetId="3"/>
-    <sheet name="Sale-Void" r:id="rId4" sheetId="4"/>
-    <sheet name="Sale-Credit" r:id="rId5" sheetId="5"/>
-    <sheet name="Sale-Unencrypted" r:id="rId6" sheetId="6"/>
-    <sheet name="Sale-ZeroDollar" r:id="rId7" sheetId="7"/>
-    <sheet name="Sale-Void-NoTranxID" r:id="rId8" sheetId="8"/>
-    <sheet name="Sale-Credit-Void" r:id="rId9" sheetId="9"/>
-    <sheet name="Auth-Cap-Void" r:id="rId10" sheetId="10"/>
-    <sheet name="Auth-Cap-Credit" r:id="rId11" sheetId="11"/>
-    <sheet name="Sale-Encrypted" r:id="rId12" sheetId="12"/>
-    <sheet name="Sale-MRF" r:id="rId13" sheetId="13"/>
-    <sheet name="Auth-MRF" r:id="rId14" sheetId="14"/>
-    <sheet name="Cap-MRF" r:id="rId15" sheetId="15"/>
-    <sheet name="Void-MRF" r:id="rId16" sheetId="16"/>
-    <sheet name="Credit-MRF" r:id="rId17" sheetId="17"/>
-    <sheet name="Sale-CardNotAccepted" r:id="rId18" sheetId="18"/>
-    <sheet name="Auth-CardNotAccepted" r:id="rId19" sheetId="19"/>
-    <sheet name="CreditClient" r:id="rId20" sheetId="20"/>
+    <sheet name="Auth" sheetId="1" r:id="rId1"/>
+    <sheet name="AuthCapture" sheetId="2" r:id="rId2"/>
+    <sheet name="Sale" sheetId="3" r:id="rId3"/>
+    <sheet name="Sale-Void" sheetId="4" r:id="rId4"/>
+    <sheet name="Sale-Credit" sheetId="5" r:id="rId5"/>
+    <sheet name="Sale-Unencrypted" sheetId="6" r:id="rId6"/>
+    <sheet name="Sale-ZeroDollar" sheetId="7" r:id="rId7"/>
+    <sheet name="Sale-Void-NoTranxID" sheetId="8" r:id="rId8"/>
+    <sheet name="Sale-Credit-Void" sheetId="9" r:id="rId9"/>
+    <sheet name="Auth-Cap-Void" sheetId="10" r:id="rId10"/>
+    <sheet name="Auth-Cap-Credit" sheetId="11" r:id="rId11"/>
+    <sheet name="Sale-Encrypted" sheetId="12" r:id="rId12"/>
+    <sheet name="Sale-MRF" sheetId="13" r:id="rId13"/>
+    <sheet name="Auth-MRF" sheetId="14" r:id="rId14"/>
+    <sheet name="Cap-MRF" sheetId="15" r:id="rId15"/>
+    <sheet name="Void-MRF" sheetId="16" r:id="rId16"/>
+    <sheet name="Credit-MRF" sheetId="17" r:id="rId17"/>
+    <sheet name="Sale-CardNotAccepted" sheetId="18" r:id="rId18"/>
+    <sheet name="Auth-CardNotAccepted" sheetId="19" r:id="rId19"/>
+    <sheet name="CreditClient" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3662" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="295">
   <si>
     <t>Result</t>
   </si>
@@ -492,914 +492,460 @@
     <t>4761739001010135</t>
   </si>
   <si>
-    <t>Fri Dec 12 20:24:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:25:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:25:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:25:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:25:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:25:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:25:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:26:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:31:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:31:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:31:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:31:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:32:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:32:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:32:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:32:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:33:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:33:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:33:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:33:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:33:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:34:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:34:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:34:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:34:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:35:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:35:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:35:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:35:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:35:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:36:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:36:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:36:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:36:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:37:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:37:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:37:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:37:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:38:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:38:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:38:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:38:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:38:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:38:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:38:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:39:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:40:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:40:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:40:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:40:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:40:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:40:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:40:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:40:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:40:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:41:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:42:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:43:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:56:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:56:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:56:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:56:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:56:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 20:56:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:06:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:06:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:06:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:06:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:06:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:06:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:07:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:07:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:07:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:07:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:08:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:08:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:08:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:09:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:09:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:09:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:09:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:09:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:10:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:10:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:10:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:10:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:10:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:11:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:11:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:11:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:11:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:11:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:12:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:12:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:12:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:12:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:13:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:13:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:13:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:13:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:14:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:14:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:14:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:14:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:15:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:15:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:15:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:16:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:16:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Sun Dec 14 16:16:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 17:59:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 17:59:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 17:59:33 EST 2025</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:24:15 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:24:27 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:24:37 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:24:46 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:25:12 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:25:21 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:25:35 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:25:48 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:26:01 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:26:12 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:27:45 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:27:54 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:28:03 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:28:10 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:28:18 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:28:27 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:28:35 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:28:47 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:28:59 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:29:11 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:29:25 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:29:39 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:29:52 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:30:05 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:30:18 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:30:30 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:30:43 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:30:51 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:31:00 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:31:08 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:31:15 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:31:22 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:31:30 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:31:37 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:31:45 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:31:57 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:32:10 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:32:23 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:32:48 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:33:01 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:33:19 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:33:36 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:33:53 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:34:11 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:34:35 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:34:59 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:35:17 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:35:33 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:35:50 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:36:08 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:36:25 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:36:42 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:37:00 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:37:17 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:37:34 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:37:39 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:37:45 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:37:51 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:38:04 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:38:17 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:38:31 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:38:45 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:38:58 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:39:11 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:39:25 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:39:39 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:39:52 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:40:06 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:40:19 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:40:32 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:40:45 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:40:59 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:41:12 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:41:25 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:41:39 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:41:52 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:42:05 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:42:18 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:42:31 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:42:45 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:42:58 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:43:12 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:43:25 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:43:38 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:43:52 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:44:06 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:44:19 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:44:34 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:44:47 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:00 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:06 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:13 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:20 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:26 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:32 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:37 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:43 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:49 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:45:56 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:03 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:10 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:16 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:23 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:29 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:35 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:41 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:47 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:53 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:46:59 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:47:05 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:47:11 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:47:17 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:47:23 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:47:29 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:47:36 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:47:42 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:47:48 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:47:54 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:00 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:06 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:13 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:19 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:24 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:29 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:34 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:39 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:44 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:49 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:54 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:48:59 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:04 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:09 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:15 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:19 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:24 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:29 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:35 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:40 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:46 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:51 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:49:56 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:50:03 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:50:08 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 17:50:14 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 18:03:27 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 18:03:35 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 18:03:42 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 18:03:50 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 18:03:58 EST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 16 18:04:06 EST 2026</t>
+    <t>Fri Feb 13 21:07:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:07:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:07:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:07:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:07:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:07:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:08:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:08:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:08:38 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:08:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:09:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:09:22 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:09:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:09:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:10:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:10:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:10:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:10:42 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:10:55 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:11:09 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:11:22 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:11:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:11:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:12:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:12:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:12:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:12:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:12:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:13:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:13:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:13:38 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:13:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:14:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:14:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:14:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:14:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:14:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:15:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:15:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:15:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:15:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:15:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:15:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:15:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:15:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:15:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:33 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:16:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:17:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:17:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:17:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:17:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:17:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:17:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:17:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:17:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:17:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:18:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:19:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:09 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:33:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:33:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:33:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:34:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:34:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:34:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:56:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:56:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:56:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:56:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:56:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:56:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:57:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:57:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:57:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:57:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:58:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:58:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:58:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:58:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:58:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:58:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:58:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:59:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:59:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:59:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:59:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:00:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:00:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:00:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:00:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:00:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:01:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:01:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:01:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:01:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:01:42 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:01:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:01:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:02:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:02:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:02:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:02:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:02:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:03:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:03:22 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:03:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:03:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:04:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:04:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:04:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:05:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:05:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:05:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:06:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:06:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:06:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:07:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:07:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:07:44 EST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1448,24 +994,24 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
-    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1482,10 +1028,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1520,7 +1066,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1572,7 +1118,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1683,21 +1229,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1714,7 +1260,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1766,31 +1312,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B3BF19-5985-4984-B3CC-B3E33E12951F}">
-  <dimension ref="A1:P6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B3BF19-5985-4984-B3CC-B3E33E12951F}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1845,7 +1391,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -1892,7 +1438,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>242</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -1939,7 +1485,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>243</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -1986,7 +1532,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>244</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -2033,7 +1579,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -2076,8 +1622,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -2085,24 +1631,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2359731-E4E5-4078-88F3-04F82A8C8041}">
-  <dimension ref="A1:P6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2359731-E4E5-4078-88F3-04F82A8C8041}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -2157,7 +1703,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -2204,7 +1750,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>341</v>
+        <v>286</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -2251,7 +1797,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>342</v>
+        <v>287</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -2298,7 +1844,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>343</v>
+        <v>288</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -2345,7 +1891,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>344</v>
+        <v>289</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -2388,29 +1934,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC99232A-9CA5-4149-85DE-BA29AA7848F2}">
-  <dimension ref="A1:P6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC99232A-9CA5-4149-85DE-BA29AA7848F2}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -2465,7 +2011,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>290</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -2512,7 +2058,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>346</v>
+        <v>291</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -2559,7 +2105,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>347</v>
+        <v>292</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -2606,7 +2152,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -2653,7 +2199,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>349</v>
+        <v>294</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -2696,31 +2242,31 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F4B3B1-E8F7-45EE-B808-7340C74D1EA9}">
-  <dimension ref="A1:P4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F4B3B1-E8F7-45EE-B808-7340C74D1EA9}">
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="46.86328125" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="2" width="17.265625" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="2" width="22.86328125" collapsed="true"/>
-    <col min="16" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="46.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="17.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="22.86328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="16" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -2770,12 +2316,12 @@
         <v>38</v>
       </c>
     </row>
-    <row ht="28.5" r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>350</v>
+        <v>145</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -2817,12 +2363,12 @@
         <v>134</v>
       </c>
     </row>
-    <row ht="28.5" r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>351</v>
+        <v>146</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -2864,12 +2410,12 @@
         <v>134</v>
       </c>
     </row>
-    <row ht="28.5" r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>352</v>
+        <v>147</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -2912,33 +2458,33 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F3F3A8-CC55-49BE-B541-0DA825F10822}">
-  <dimension ref="A1:AZ34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F3F3A8-CC55-49BE-B541-0DA825F10822}">
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="12" max="12" style="2" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" style="1" width="9.1328125" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="15" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="2" collapsed="1"/>
+    <col min="13" max="13" width="9.1328125" style="1" collapsed="1"/>
+    <col min="14" max="14" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="15" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" ht="42.75" r="1" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3093,12 +2639,12 @@
         <v>75</v>
       </c>
     </row>
-    <row customFormat="1" ht="42.75" r="2" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>353</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -3213,12 +2759,12 @@
       </c>
       <c r="AY2" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="3" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>354</v>
+        <v>149</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -3333,12 +2879,12 @@
       </c>
       <c r="AY3" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="4" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>355</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -3453,12 +2999,12 @@
       </c>
       <c r="AY4" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="5" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>356</v>
+        <v>151</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -3573,12 +3119,12 @@
       </c>
       <c r="AY5" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="6" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>357</v>
+        <v>152</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -3693,12 +3239,12 @@
       </c>
       <c r="AY6" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="7" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>358</v>
+        <v>153</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -3813,12 +3359,12 @@
       </c>
       <c r="AY7" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="8" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>359</v>
+        <v>154</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -3934,12 +3480,12 @@
       </c>
       <c r="AY8" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="9" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>360</v>
+        <v>155</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -4055,12 +3601,12 @@
       </c>
       <c r="AY9" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="10" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>156</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -4176,12 +3722,12 @@
       </c>
       <c r="AY10" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="11" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>362</v>
+        <v>157</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -4296,12 +3842,12 @@
       </c>
       <c r="AY11" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="12" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>363</v>
+        <v>158</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
@@ -4416,12 +3962,12 @@
       </c>
       <c r="AY12" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="13" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>364</v>
+        <v>159</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>20</v>
@@ -4536,12 +4082,12 @@
       </c>
       <c r="AY13" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="14" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>365</v>
+        <v>160</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -4656,12 +4202,12 @@
       </c>
       <c r="AY14" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="15" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>366</v>
+        <v>161</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>20</v>
@@ -4776,12 +4322,12 @@
       </c>
       <c r="AY15" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="16" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>367</v>
+        <v>162</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
@@ -4896,12 +4442,12 @@
       </c>
       <c r="AY16" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="17" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>368</v>
+        <v>163</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>20</v>
@@ -5016,12 +4562,12 @@
       </c>
       <c r="AY17" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="18" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>369</v>
+        <v>164</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>20</v>
@@ -5136,12 +4682,12 @@
       </c>
       <c r="AY18" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="19" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>370</v>
+        <v>165</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>20</v>
@@ -5256,12 +4802,12 @@
       </c>
       <c r="AY19" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="20" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>371</v>
+        <v>166</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
@@ -5376,12 +4922,12 @@
       </c>
       <c r="AY20" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="21" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>372</v>
+        <v>167</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>20</v>
@@ -5496,12 +5042,12 @@
       </c>
       <c r="AY21" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="22" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>373</v>
+        <v>168</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
@@ -5616,12 +5162,12 @@
       </c>
       <c r="AY22" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="23" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>374</v>
+        <v>169</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -5736,12 +5282,12 @@
       </c>
       <c r="AY23" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="24" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>375</v>
+        <v>170</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>20</v>
@@ -5856,12 +5402,12 @@
       </c>
       <c r="AY24" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="25" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>376</v>
+        <v>171</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -5976,12 +5522,12 @@
       </c>
       <c r="AY25" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="26" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>377</v>
+        <v>172</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -6096,12 +5642,12 @@
       </c>
       <c r="AY26" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="27" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>378</v>
+        <v>173</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
@@ -6216,12 +5762,12 @@
       </c>
       <c r="AY27" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="28" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>379</v>
+        <v>174</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>20</v>
@@ -6336,12 +5882,12 @@
       </c>
       <c r="AY28" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="29" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>380</v>
+        <v>175</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -6456,12 +6002,12 @@
       </c>
       <c r="AY29" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="30" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>381</v>
+        <v>176</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
@@ -6576,12 +6122,12 @@
       </c>
       <c r="AY30" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="31" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>382</v>
+        <v>177</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>20</v>
@@ -6696,12 +6242,12 @@
       </c>
       <c r="AY31" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="32" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>383</v>
+        <v>178</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>20</v>
@@ -6816,12 +6362,12 @@
       </c>
       <c r="AY32" s="4"/>
     </row>
-    <row customFormat="1" ht="42.75" r="33" s="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>384</v>
+        <v>179</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>20</v>
@@ -6940,33 +6486,33 @@
       <c r="L34" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EF3280-CA4E-46F2-B2B8-2F43A765033A}">
-  <dimension ref="A1:W34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EF3280-CA4E-46F2-B2B8-2F43A765033A}">
+  <dimension ref="A1:V34"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="12" max="12" style="2" width="9.1328125" collapsed="true"/>
-    <col min="13" max="14" customWidth="true" style="2" width="11.265625" collapsed="true"/>
-    <col min="15" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="2" collapsed="1"/>
+    <col min="13" max="14" width="11.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="15" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" ht="28.5" r="1" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7034,12 +6580,12 @@
         <v>55</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>385</v>
+        <v>180</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -7099,12 +6645,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>386</v>
+        <v>181</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -7164,12 +6710,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="4" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>387</v>
+        <v>182</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -7229,12 +6775,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="5" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>388</v>
+        <v>183</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -7294,12 +6840,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="6" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>389</v>
+        <v>184</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -7359,12 +6905,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="7" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>390</v>
+        <v>185</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -7424,12 +6970,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="8" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>391</v>
+        <v>186</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -7490,12 +7036,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="9" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>392</v>
+        <v>187</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -7556,12 +7102,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="10" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>393</v>
+        <v>188</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -7622,12 +7168,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="11" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>394</v>
+        <v>189</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -7687,12 +7233,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="12" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>395</v>
+        <v>190</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
@@ -7752,12 +7298,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="13" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>396</v>
+        <v>191</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>20</v>
@@ -7817,12 +7363,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="14" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>397</v>
+        <v>192</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -7882,12 +7428,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="15" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>398</v>
+        <v>193</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>20</v>
@@ -7947,12 +7493,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="16" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>399</v>
+        <v>194</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
@@ -8012,12 +7558,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="17" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>400</v>
+        <v>195</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>20</v>
@@ -8077,12 +7623,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="18" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>401</v>
+        <v>196</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>20</v>
@@ -8142,12 +7688,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="19" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>402</v>
+        <v>197</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>20</v>
@@ -8207,12 +7753,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="20" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>403</v>
+        <v>198</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
@@ -8272,12 +7818,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="21" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>404</v>
+        <v>199</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>20</v>
@@ -8337,12 +7883,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="22" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>405</v>
+        <v>200</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
@@ -8402,12 +7948,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="23" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>406</v>
+        <v>201</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -8467,12 +8013,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="24" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>407</v>
+        <v>202</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>20</v>
@@ -8532,12 +8078,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="25" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>408</v>
+        <v>203</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -8597,12 +8143,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="26" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>409</v>
+        <v>204</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -8662,12 +8208,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="27" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>410</v>
+        <v>205</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
@@ -8727,12 +8273,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="28" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>411</v>
+        <v>206</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>20</v>
@@ -8792,12 +8338,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="29" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>412</v>
+        <v>207</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -8857,12 +8403,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="30" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>413</v>
+        <v>208</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
@@ -8922,12 +8468,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="31" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>414</v>
+        <v>209</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>20</v>
@@ -8987,12 +8533,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="32" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>415</v>
+        <v>210</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>20</v>
@@ -9052,12 +8598,12 @@
         <v>89</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="33" s="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>416</v>
+        <v>211</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>20</v>
@@ -9121,30 +8667,30 @@
       <c r="L34" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA243B-4AA6-4B80-8D83-694CE3832665}">
-  <dimension ref="A1:N10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA243B-4AA6-4B80-8D83-694CE3832665}">
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="11" max="12" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="13" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9185,12 +8731,12 @@
         <v>5</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>417</v>
+        <v>212</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -9223,12 +8769,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>418</v>
+        <v>213</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -9261,12 +8807,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="4" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>419</v>
+        <v>214</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -9300,12 +8846,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="5" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>420</v>
+        <v>215</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -9338,12 +8884,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="6" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>421</v>
+        <v>216</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -9381,7 +8927,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>422</v>
+        <v>217</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -9419,7 +8965,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>423</v>
+        <v>218</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9457,7 +9003,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>219</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -9494,30 +9040,30 @@
       <c r="I10" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9035B600-1AE4-4F39-B9B0-C3B647778074}">
-  <dimension ref="A1:M9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9035B600-1AE4-4F39-B9B0-C3B647778074}">
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="11" max="12" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="13" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9555,12 +9101,12 @@
         <v>124</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>425</v>
+        <v>220</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -9590,12 +9136,12 @@
         <v>125</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>426</v>
+        <v>221</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -9625,12 +9171,12 @@
         <v>125</v>
       </c>
     </row>
-    <row customFormat="1" r="4" s="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>427</v>
+        <v>222</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -9661,12 +9207,12 @@
         <v>125</v>
       </c>
     </row>
-    <row customFormat="1" r="5" s="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>428</v>
+        <v>223</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -9701,7 +9247,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>429</v>
+        <v>224</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -9736,7 +9282,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>430</v>
+        <v>225</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -9771,7 +9317,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>431</v>
+        <v>226</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9805,30 +9351,30 @@
       <c r="I9" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D985158-3685-4E06-8AAF-5C6291ED2A2E}">
-  <dimension ref="A1:N10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D985158-3685-4E06-8AAF-5C6291ED2A2E}">
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="11" max="12" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="13" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9869,12 +9415,12 @@
         <v>5</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>432</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -9907,12 +9453,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>433</v>
+        <v>228</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -9945,12 +9491,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="4" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>434</v>
+        <v>229</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -9984,12 +9530,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="5" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>435</v>
+        <v>230</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -10022,12 +9568,12 @@
         <v>86</v>
       </c>
     </row>
-    <row customFormat="1" r="6" s="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>436</v>
+        <v>231</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -10065,7 +9611,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>437</v>
+        <v>232</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -10103,7 +9649,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>438</v>
+        <v>233</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -10141,7 +9687,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>439</v>
+        <v>234</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -10178,29 +9724,29 @@
       <c r="I10" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A3FE28-6D3A-468C-B453-4E8625D9142D}">
-  <dimension ref="A1:P4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A3FE28-6D3A-468C-B453-4E8625D9142D}">
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="24.265625" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="24.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -10255,7 +9801,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>443</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
@@ -10293,7 +9839,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>444</v>
+        <v>239</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>129</v>
@@ -10331,7 +9877,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>445</v>
+        <v>240</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>129</v>
@@ -10365,29 +9911,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C12825-4D21-4476-8848-6E435EC04842}">
-  <dimension ref="A1:P4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C12825-4D21-4476-8848-6E435EC04842}">
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="30.59765625" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="30.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -10442,7 +9988,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>440</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
@@ -10480,7 +10026,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>441</v>
+        <v>236</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>129</v>
@@ -10518,7 +10064,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>442</v>
+        <v>237</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>129</v>
@@ -10552,29 +10098,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77641590-759F-4E9F-886E-0EE016894C97}">
-  <dimension ref="A1:P6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77641590-759F-4E9F-886E-0EE016894C97}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -10629,7 +10175,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>246</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -10676,7 +10222,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -10723,7 +10269,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>303</v>
+        <v>248</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -10770,7 +10316,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>304</v>
+        <v>249</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -10817,7 +10363,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -10860,7 +10406,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -10868,22 +10414,22 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DCF843-7CC4-48A5-8072-F1A801B90CE0}">
-  <dimension ref="A1:L2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DCF843-7CC4-48A5-8072-F1A801B90CE0}">
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="21.0" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="21.3984375" collapsed="true"/>
-    <col min="10" max="10" style="2" width="9.1328125" collapsed="true"/>
-    <col min="11" max="11" style="1" width="9.1328125" collapsed="true"/>
-    <col min="12" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="21" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="21.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="9.1328125" style="2" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="1" collapsed="1"/>
+    <col min="12" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
@@ -10954,29 +10500,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F862F746-9284-4D5F-8449-DC04488EA2C6}">
-  <dimension ref="A1:P7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F862F746-9284-4D5F-8449-DC04488EA2C6}">
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="18.59765625" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="18.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -11031,7 +10577,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -11078,7 +10624,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>252</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -11125,7 +10671,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>308</v>
+        <v>253</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -11172,7 +10718,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -11219,7 +10765,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>310</v>
+        <v>255</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -11266,7 +10812,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>256</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>136</v>
@@ -11309,29 +10855,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD14A431-43B3-4E34-B368-8DDA4A423BE8}">
-  <dimension ref="A1:P6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD14A431-43B3-4E34-B368-8DDA4A423BE8}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -11386,7 +10932,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -11433,7 +10979,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>258</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -11480,7 +11026,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>259</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -11527,7 +11073,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -11574,7 +11120,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>261</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -11617,29 +11163,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDEE7-E2F6-498C-8E90-D24ED0C44AC2}">
-  <dimension ref="A1:P6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDEE7-E2F6-498C-8E90-D24ED0C44AC2}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -11694,7 +11240,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>262</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -11741,7 +11287,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>263</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -11788,7 +11334,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>264</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -11835,7 +11381,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>265</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -11882,7 +11428,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>321</v>
+        <v>266</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -11925,29 +11471,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C85066F-A70F-4EC6-96A2-3B11D71E8332}">
-  <dimension ref="A1:N4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C85066F-A70F-4EC6-96A2-3B11D71E8332}">
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="46.86328125" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="46.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -11991,12 +11537,12 @@
         <v>35</v>
       </c>
     </row>
-    <row ht="42.75" r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>322</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -12032,12 +11578,12 @@
         <v>135</v>
       </c>
     </row>
-    <row ht="42.75" r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>323</v>
+        <v>268</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -12073,12 +11619,12 @@
         <v>135</v>
       </c>
     </row>
-    <row ht="42.75" r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>324</v>
+        <v>269</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -12115,29 +11661,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA94AF-A176-4725-8452-BA8E3503AAAB}">
-  <dimension ref="A1:P6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA94AF-A176-4725-8452-BA8E3503AAAB}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -12192,7 +11738,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>270</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -12239,7 +11785,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>271</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -12286,7 +11832,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>327</v>
+        <v>272</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -12333,7 +11879,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -12380,7 +11926,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>329</v>
+        <v>274</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -12423,29 +11969,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407A61CA-7BCD-4622-83EC-6EE78F45F1F1}">
-  <dimension ref="A1:P6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407A61CA-7BCD-4622-83EC-6EE78F45F1F1}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -12500,7 +12046,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>275</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -12547,7 +12093,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>331</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -12594,7 +12140,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>332</v>
+        <v>277</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -12641,7 +12187,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -12688,7 +12234,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>334</v>
+        <v>279</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -12731,29 +12277,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846A7054-8630-44CB-A36C-72BF4E3BB15C}">
-  <dimension ref="A1:P6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846A7054-8630-44CB-A36C-72BF4E3BB15C}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
-    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
-    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
+    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
+    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
+    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
+    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
+    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -12808,7 +12354,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -12855,7 +12401,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>336</v>
+        <v>281</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -12902,7 +12448,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>337</v>
+        <v>282</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -12949,7 +12495,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>338</v>
+        <v>283</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -12996,7 +12542,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>284</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -13039,6 +12585,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/VLinkSmokeData.xlsx
+++ b/KatalonData/VLinkSmokeData.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B75DAD-2D41-47E3-A99D-5900C500CD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{78B75DAD-2D41-47E3-A99D-5900C500CD8A}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="48312" yWindow="5352" windowWidth="26556" windowHeight="12228" tabRatio="887" activeTab="2" xr2:uid="{D3A86137-2393-48B3-A2A1-24E657E7CF34}"/>
+    <workbookView activeTab="2" tabRatio="887" windowHeight="12228" windowWidth="26556" xWindow="48312" xr2:uid="{D3A86137-2393-48B3-A2A1-24E657E7CF34}" yWindow="5352"/>
   </bookViews>
   <sheets>
-    <sheet name="Auth" sheetId="1" r:id="rId1"/>
-    <sheet name="AuthCapture" sheetId="2" r:id="rId2"/>
-    <sheet name="Sale" sheetId="3" r:id="rId3"/>
-    <sheet name="Sale-Void" sheetId="4" r:id="rId4"/>
-    <sheet name="Sale-Credit" sheetId="5" r:id="rId5"/>
-    <sheet name="Sale-Unencrypted" sheetId="6" r:id="rId6"/>
-    <sheet name="Sale-ZeroDollar" sheetId="7" r:id="rId7"/>
-    <sheet name="Sale-Void-NoTranxID" sheetId="8" r:id="rId8"/>
-    <sheet name="Sale-Credit-Void" sheetId="9" r:id="rId9"/>
-    <sheet name="Auth-Cap-Void" sheetId="10" r:id="rId10"/>
-    <sheet name="Auth-Cap-Credit" sheetId="11" r:id="rId11"/>
-    <sheet name="Sale-Encrypted" sheetId="12" r:id="rId12"/>
-    <sheet name="Sale-MRF" sheetId="13" r:id="rId13"/>
-    <sheet name="Auth-MRF" sheetId="14" r:id="rId14"/>
-    <sheet name="Cap-MRF" sheetId="15" r:id="rId15"/>
-    <sheet name="Void-MRF" sheetId="16" r:id="rId16"/>
-    <sheet name="Credit-MRF" sheetId="17" r:id="rId17"/>
-    <sheet name="Sale-CardNotAccepted" sheetId="18" r:id="rId18"/>
-    <sheet name="Auth-CardNotAccepted" sheetId="19" r:id="rId19"/>
-    <sheet name="CreditClient" sheetId="20" r:id="rId20"/>
+    <sheet name="Auth" r:id="rId1" sheetId="1"/>
+    <sheet name="AuthCapture" r:id="rId2" sheetId="2"/>
+    <sheet name="Sale" r:id="rId3" sheetId="3"/>
+    <sheet name="Sale-Void" r:id="rId4" sheetId="4"/>
+    <sheet name="Sale-Credit" r:id="rId5" sheetId="5"/>
+    <sheet name="Sale-Unencrypted" r:id="rId6" sheetId="6"/>
+    <sheet name="Sale-ZeroDollar" r:id="rId7" sheetId="7"/>
+    <sheet name="Sale-Void-NoTranxID" r:id="rId8" sheetId="8"/>
+    <sheet name="Sale-Credit-Void" r:id="rId9" sheetId="9"/>
+    <sheet name="Auth-Cap-Void" r:id="rId10" sheetId="10"/>
+    <sheet name="Auth-Cap-Credit" r:id="rId11" sheetId="11"/>
+    <sheet name="Sale-Encrypted" r:id="rId12" sheetId="12"/>
+    <sheet name="Sale-MRF" r:id="rId13" sheetId="13"/>
+    <sheet name="Auth-MRF" r:id="rId14" sheetId="14"/>
+    <sheet name="Cap-MRF" r:id="rId15" sheetId="15"/>
+    <sheet name="Void-MRF" r:id="rId16" sheetId="16"/>
+    <sheet name="Credit-MRF" r:id="rId17" sheetId="17"/>
+    <sheet name="Sale-CardNotAccepted" r:id="rId18" sheetId="18"/>
+    <sheet name="Auth-CardNotAccepted" r:id="rId19" sheetId="19"/>
+    <sheet name="CreditClient" r:id="rId20" sheetId="20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3362" uniqueCount="445">
   <si>
     <t>Result</t>
   </si>
@@ -940,12 +940,463 @@
   </si>
   <si>
     <t>Sat Feb 14 13:07:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:28:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:29:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:29:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:29:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:29:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:29:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:30:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:30:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:30:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:31:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:32:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:32:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:32:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:32:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:33:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:33:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:33:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:33:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:34:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:34:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:34:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:34:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:35:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:35:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:35:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:35:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:36:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:36:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:36:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:36:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:36:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:37:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:37:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:37:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:37:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:37:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:38:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:38:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:39:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:39:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:39:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:40:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:40:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:41:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:41:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:42:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:42:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:42:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:43:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:43:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:44:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:44:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:44:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:45:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:45:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:45:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:45:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:46:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:46:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:46:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:46:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:47:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:47:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:47:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:47:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:48:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:48:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:48:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:49:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:49:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:49:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:49:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:50:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:50:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:50:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:50:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:51:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:51:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:51:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:51:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:52:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:52:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:52:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:53:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:53:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:53:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:53:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:54:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:54:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:54:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:54:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:55:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:55:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:55:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:55:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:55:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:56:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:56:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:56:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:56:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:56:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:56:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:57:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:57:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:57:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:57:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:57:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:58:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:58:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:58:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:59:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:59:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:59:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 13:59:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:00:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:00:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:00:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:00:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:00:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:00:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:00:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:00:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:01:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:01:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:01:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:01:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:01:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:01:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:01:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:01:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:02:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:02:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:02:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:02:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:02:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:02:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:02:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:02:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:02:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:03:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:03:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:03:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:03:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:03:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:20:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:20:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:20:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:21:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:21:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:21:19 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -994,24 +1445,24 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1028,10 +1479,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1066,7 +1517,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1118,7 +1569,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1229,21 +1680,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1260,7 +1711,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1312,31 +1763,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B3BF19-5985-4984-B3CC-B3E33E12951F}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B3BF19-5985-4984-B3CC-B3E33E12951F}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1391,7 +1842,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -1438,7 +1889,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>296</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -1485,7 +1936,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>297</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -1532,7 +1983,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1579,7 +2030,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>299</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -1622,8 +2073,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1631,24 +2082,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2359731-E4E5-4078-88F3-04F82A8C8041}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2359731-E4E5-4078-88F3-04F82A8C8041}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1703,7 +2154,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>339</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -1750,7 +2201,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>340</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -1797,7 +2248,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>341</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -1844,7 +2295,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>342</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -1891,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>343</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -1934,29 +2385,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC99232A-9CA5-4149-85DE-BA29AA7848F2}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC99232A-9CA5-4149-85DE-BA29AA7848F2}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -2011,7 +2462,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>290</v>
+        <v>344</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -2058,7 +2509,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>291</v>
+        <v>345</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -2105,7 +2556,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -2152,7 +2603,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>293</v>
+        <v>347</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -2199,7 +2650,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -2242,31 +2693,31 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F4B3B1-E8F7-45EE-B808-7340C74D1EA9}">
-  <dimension ref="A1:O4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F4B3B1-E8F7-45EE-B808-7340C74D1EA9}">
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="46.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="17.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="22.86328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="16" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="46.86328125" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="2" width="17.265625" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="2" width="22.86328125" collapsed="true"/>
+    <col min="16" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -2316,12 +2767,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
+    <row ht="28.5" r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>349</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -2363,12 +2814,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
+    <row ht="28.5" r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>350</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -2410,12 +2861,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="28.5" x14ac:dyDescent="0.45">
+    <row ht="28.5" r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>351</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -2458,33 +2909,33 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F3F3A8-CC55-49BE-B541-0DA825F10822}">
-  <dimension ref="A1:AY34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F3F3A8-CC55-49BE-B541-0DA825F10822}">
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="2" collapsed="1"/>
-    <col min="13" max="13" width="9.1328125" style="1" collapsed="1"/>
-    <col min="14" max="14" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="12" max="12" style="2" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" style="1" width="9.1328125" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="15" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="1" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2639,12 +3090,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="2" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>352</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -2759,12 +3210,12 @@
       </c>
       <c r="AY2" s="4"/>
     </row>
-    <row r="3" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="3" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>353</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -2879,12 +3330,12 @@
       </c>
       <c r="AY3" s="4"/>
     </row>
-    <row r="4" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="4" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>354</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -2999,12 +3450,12 @@
       </c>
       <c r="AY4" s="4"/>
     </row>
-    <row r="5" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="5" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>355</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -3119,12 +3570,12 @@
       </c>
       <c r="AY5" s="4"/>
     </row>
-    <row r="6" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="6" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>356</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -3239,12 +3690,12 @@
       </c>
       <c r="AY6" s="4"/>
     </row>
-    <row r="7" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="7" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>357</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -3359,12 +3810,12 @@
       </c>
       <c r="AY7" s="4"/>
     </row>
-    <row r="8" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="8" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>358</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -3480,12 +3931,12 @@
       </c>
       <c r="AY8" s="4"/>
     </row>
-    <row r="9" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="9" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>359</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -3601,12 +4052,12 @@
       </c>
       <c r="AY9" s="4"/>
     </row>
-    <row r="10" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="10" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>360</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -3722,12 +4173,12 @@
       </c>
       <c r="AY10" s="4"/>
     </row>
-    <row r="11" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="11" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>157</v>
+        <v>361</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -3842,12 +4293,12 @@
       </c>
       <c r="AY11" s="4"/>
     </row>
-    <row r="12" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="12" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>362</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
@@ -3962,12 +4413,12 @@
       </c>
       <c r="AY12" s="4"/>
     </row>
-    <row r="13" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="13" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>363</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>20</v>
@@ -4082,12 +4533,12 @@
       </c>
       <c r="AY13" s="4"/>
     </row>
-    <row r="14" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="14" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>364</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -4202,12 +4653,12 @@
       </c>
       <c r="AY14" s="4"/>
     </row>
-    <row r="15" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="15" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>365</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>20</v>
@@ -4322,12 +4773,12 @@
       </c>
       <c r="AY15" s="4"/>
     </row>
-    <row r="16" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="16" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
@@ -4442,12 +4893,12 @@
       </c>
       <c r="AY16" s="4"/>
     </row>
-    <row r="17" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="17" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>163</v>
+        <v>367</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>20</v>
@@ -4562,12 +5013,12 @@
       </c>
       <c r="AY17" s="4"/>
     </row>
-    <row r="18" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="18" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>164</v>
+        <v>368</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>20</v>
@@ -4682,12 +5133,12 @@
       </c>
       <c r="AY18" s="4"/>
     </row>
-    <row r="19" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="19" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>369</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>20</v>
@@ -4802,12 +5253,12 @@
       </c>
       <c r="AY19" s="4"/>
     </row>
-    <row r="20" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="20" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>370</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
@@ -4922,12 +5373,12 @@
       </c>
       <c r="AY20" s="4"/>
     </row>
-    <row r="21" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="21" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>167</v>
+        <v>371</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>20</v>
@@ -5042,12 +5493,12 @@
       </c>
       <c r="AY21" s="4"/>
     </row>
-    <row r="22" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="22" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>168</v>
+        <v>372</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
@@ -5162,12 +5613,12 @@
       </c>
       <c r="AY22" s="4"/>
     </row>
-    <row r="23" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="23" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>169</v>
+        <v>373</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -5282,12 +5733,12 @@
       </c>
       <c r="AY23" s="4"/>
     </row>
-    <row r="24" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="24" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>170</v>
+        <v>374</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>20</v>
@@ -5402,12 +5853,12 @@
       </c>
       <c r="AY24" s="4"/>
     </row>
-    <row r="25" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="25" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>375</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -5522,12 +5973,12 @@
       </c>
       <c r="AY25" s="4"/>
     </row>
-    <row r="26" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="26" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>376</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -5642,12 +6093,12 @@
       </c>
       <c r="AY26" s="4"/>
     </row>
-    <row r="27" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="27" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>377</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
@@ -5762,12 +6213,12 @@
       </c>
       <c r="AY27" s="4"/>
     </row>
-    <row r="28" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="28" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>174</v>
+        <v>378</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>20</v>
@@ -5882,12 +6333,12 @@
       </c>
       <c r="AY28" s="4"/>
     </row>
-    <row r="29" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="29" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>379</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -6002,12 +6453,12 @@
       </c>
       <c r="AY29" s="4"/>
     </row>
-    <row r="30" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="30" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>176</v>
+        <v>380</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
@@ -6122,12 +6573,12 @@
       </c>
       <c r="AY30" s="4"/>
     </row>
-    <row r="31" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="31" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>381</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>20</v>
@@ -6242,12 +6693,12 @@
       </c>
       <c r="AY31" s="4"/>
     </row>
-    <row r="32" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="32" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>382</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>20</v>
@@ -6362,12 +6813,12 @@
       </c>
       <c r="AY32" s="4"/>
     </row>
-    <row r="33" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="42.75" r="33" s="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>383</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>20</v>
@@ -6486,33 +6937,33 @@
       <c r="L34" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EF3280-CA4E-46F2-B2B8-2F43A765033A}">
-  <dimension ref="A1:V34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EF3280-CA4E-46F2-B2B8-2F43A765033A}">
+  <dimension ref="A1:W34"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="2" collapsed="1"/>
-    <col min="13" max="14" width="11.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="15" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="12" max="12" style="2" width="9.1328125" collapsed="true"/>
+    <col min="13" max="14" customWidth="true" style="2" width="11.265625" collapsed="true"/>
+    <col min="15" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="1" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6580,12 +7031,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>384</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -6645,12 +7096,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>385</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -6710,12 +7161,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="4" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>386</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -6775,12 +7226,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="5" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>387</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -6840,12 +7291,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="6" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>388</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -6905,12 +7356,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="7" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>185</v>
+        <v>389</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -6970,12 +7421,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="8" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>390</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -7036,12 +7487,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="9" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>391</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -7102,12 +7553,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="10" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>392</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -7168,12 +7619,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="11" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>393</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
@@ -7233,12 +7684,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="12" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>394</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
@@ -7298,12 +7749,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="13" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>395</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>20</v>
@@ -7363,12 +7814,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="14" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>396</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -7428,12 +7879,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="15" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>397</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>20</v>
@@ -7493,12 +7944,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="16" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>194</v>
+        <v>398</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
@@ -7558,12 +8009,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="17" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>195</v>
+        <v>399</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>20</v>
@@ -7623,12 +8074,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="18" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>196</v>
+        <v>400</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>20</v>
@@ -7688,12 +8139,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="19" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>197</v>
+        <v>401</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>20</v>
@@ -7753,12 +8204,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="20" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>402</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
@@ -7818,12 +8269,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="21" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
+        <v>403</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>20</v>
@@ -7883,12 +8334,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="22" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>200</v>
+        <v>404</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
@@ -7948,12 +8399,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="23" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>405</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -8013,12 +8464,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="24" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>202</v>
+        <v>406</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>20</v>
@@ -8078,12 +8529,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="25" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>407</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -8143,12 +8594,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="26" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>204</v>
+        <v>408</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -8208,12 +8659,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="27" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>205</v>
+        <v>409</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
@@ -8273,12 +8724,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="28" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>206</v>
+        <v>410</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>20</v>
@@ -8338,12 +8789,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="29" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>207</v>
+        <v>411</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -8403,12 +8854,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="30" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>208</v>
+        <v>412</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
@@ -8468,12 +8919,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="31" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>209</v>
+        <v>413</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>20</v>
@@ -8533,12 +8984,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="32" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>414</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>20</v>
@@ -8598,12 +9049,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:22" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="33" s="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>415</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>20</v>
@@ -8667,30 +9118,30 @@
       <c r="L34" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA243B-4AA6-4B80-8D83-694CE3832665}">
-  <dimension ref="A1:M10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA243B-4AA6-4B80-8D83-694CE3832665}">
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="12" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="13" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="1" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8731,12 +9182,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>212</v>
+        <v>416</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -8769,12 +9220,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>417</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -8807,12 +9258,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="4" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>418</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -8846,12 +9297,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="5" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>419</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -8884,12 +9335,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="6" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>420</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -8927,7 +9378,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>421</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -8965,7 +9416,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>422</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9003,7 +9454,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>219</v>
+        <v>423</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -9040,30 +9491,30 @@
       <c r="I10" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9035B600-1AE4-4F39-B9B0-C3B647778074}">
-  <dimension ref="A1:L9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9035B600-1AE4-4F39-B9B0-C3B647778074}">
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="12" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="13" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="1" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9101,12 +9552,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>424</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -9136,12 +9587,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>425</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -9171,12 +9622,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="4" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>426</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -9207,12 +9658,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="5" s="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>223</v>
+        <v>427</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -9247,7 +9698,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>428</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -9282,7 +9733,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>429</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -9317,7 +9768,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>430</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9351,30 +9802,30 @@
       <c r="I9" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D985158-3685-4E06-8AAF-5C6291ED2A2E}">
-  <dimension ref="A1:M10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D985158-3685-4E06-8AAF-5C6291ED2A2E}">
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="12" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="28.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="11" max="12" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="13" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="1" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9415,12 +9866,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="2" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>431</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -9453,12 +9904,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row customFormat="1" ht="28.5" r="3" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>432</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -9491,12 +9942,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="4" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>433</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
@@ -9530,12 +9981,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="5" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>434</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -9568,12 +10019,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row customFormat="1" r="6" s="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>435</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
@@ -9611,7 +10062,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>436</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -9649,7 +10100,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>437</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -9687,7 +10138,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>438</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -9724,29 +10175,29 @@
       <c r="I10" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A3FE28-6D3A-468C-B453-4E8625D9142D}">
-  <dimension ref="A1:O4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A3FE28-6D3A-468C-B453-4E8625D9142D}">
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="24.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="24.265625" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -9801,7 +10252,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>442</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
@@ -9839,7 +10290,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>443</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>129</v>
@@ -9877,7 +10328,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>444</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>129</v>
@@ -9911,29 +10362,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C12825-4D21-4476-8848-6E435EC04842}">
-  <dimension ref="A1:O4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C12825-4D21-4476-8848-6E435EC04842}">
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="30.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="30.59765625" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -9988,7 +10439,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>439</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>129</v>
@@ -10026,7 +10477,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>440</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>129</v>
@@ -10064,7 +10515,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>441</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>129</v>
@@ -10098,29 +10549,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77641590-759F-4E9F-886E-0EE016894C97}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77641590-759F-4E9F-886E-0EE016894C97}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -10175,7 +10626,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>300</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -10222,7 +10673,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>247</v>
+        <v>301</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -10269,7 +10720,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>302</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -10316,7 +10767,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>249</v>
+        <v>303</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -10363,7 +10814,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>250</v>
+        <v>304</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -10406,7 +10857,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -10414,22 +10865,22 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DCF843-7CC4-48A5-8072-F1A801B90CE0}">
-  <dimension ref="A1:K2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DCF843-7CC4-48A5-8072-F1A801B90CE0}">
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="21" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="21.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="9.1328125" style="2" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="1" collapsed="1"/>
-    <col min="12" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="21.0" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="21.3984375" collapsed="true"/>
+    <col min="10" max="10" style="2" width="9.1328125" collapsed="true"/>
+    <col min="11" max="11" style="1" width="9.1328125" collapsed="true"/>
+    <col min="12" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
@@ -10500,29 +10951,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F862F746-9284-4D5F-8449-DC04488EA2C6}">
-  <dimension ref="A1:O7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F862F746-9284-4D5F-8449-DC04488EA2C6}">
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="18.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="18.59765625" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -10577,7 +11028,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>305</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -10624,7 +11075,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>306</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -10671,7 +11122,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>307</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -10718,7 +11169,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>254</v>
+        <v>308</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -10765,7 +11216,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -10812,7 +11263,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>310</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>136</v>
@@ -10855,29 +11306,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD14A431-43B3-4E34-B368-8DDA4A423BE8}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD14A431-43B3-4E34-B368-8DDA4A423BE8}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -10932,7 +11383,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -10979,7 +11430,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -11026,7 +11477,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>313</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -11073,7 +11524,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>314</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -11120,7 +11571,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>315</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -11163,29 +11614,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDEE7-E2F6-498C-8E90-D24ED0C44AC2}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8FDEE7-E2F6-498C-8E90-D24ED0C44AC2}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -11240,7 +11691,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>316</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -11287,7 +11738,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -11334,7 +11785,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -11381,7 +11832,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -11428,7 +11879,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>320</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -11471,29 +11922,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C85066F-A70F-4EC6-96A2-3B11D71E8332}">
-  <dimension ref="A1:M4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C85066F-A70F-4EC6-96A2-3B11D71E8332}">
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="46.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="46.86328125" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -11537,12 +11988,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
+    <row ht="42.75" r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>267</v>
+        <v>321</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -11578,12 +12029,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
+    <row ht="42.75" r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>268</v>
+        <v>322</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -11619,12 +12070,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
+    <row ht="42.75" r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -11661,29 +12112,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA94AF-A176-4725-8452-BA8E3503AAAB}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EA94AF-A176-4725-8452-BA8E3503AAAB}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -11738,7 +12189,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -11785,7 +12236,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>325</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -11832,7 +12283,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -11879,7 +12330,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>327</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -11926,7 +12377,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -11969,29 +12420,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407A61CA-7BCD-4622-83EC-6EE78F45F1F1}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407A61CA-7BCD-4622-83EC-6EE78F45F1F1}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -12046,7 +12497,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>329</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -12093,7 +12544,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>330</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -12140,7 +12591,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>331</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -12187,7 +12638,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -12234,7 +12685,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>333</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -12277,29 +12728,29 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846A7054-8630-44CB-A36C-72BF4E3BB15C}">
-  <dimension ref="A1:O6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846A7054-8630-44CB-A36C-72BF4E3BB15C}">
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="2" collapsed="1"/>
-    <col min="2" max="2" width="27.1328125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1328125" style="2" collapsed="1"/>
-    <col min="5" max="5" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="13.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.1328125" style="2" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.265625" style="2" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.59765625" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.1328125" style="2" collapsed="1"/>
-    <col min="12" max="12" width="9.1328125" style="1" collapsed="1"/>
-    <col min="13" max="13" width="23.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.1328125" style="2" collapsed="1"/>
+    <col min="1" max="1" style="2" width="9.1328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.1328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.1328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="14.1328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="13.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="12.1328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="18.265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="15.59765625" collapsed="true"/>
+    <col min="11" max="11" style="2" width="9.1328125" collapsed="true"/>
+    <col min="12" max="12" style="1" width="9.1328125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="23.73046875" collapsed="true"/>
+    <col min="14" max="16384" style="2" width="9.1328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -12354,7 +12805,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>334</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -12401,7 +12852,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>335</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -12448,7 +12899,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
@@ -12495,7 +12946,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
@@ -12542,7 +12993,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>284</v>
+        <v>338</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -12585,6 +13036,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>